--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D42100-E05C-4A01-B857-894301C1BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F2A04-0B28-4781-B7D1-2E760D2A3345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="451">
   <si>
     <t>id</t>
   </si>
@@ -74,16 +74,6 @@
   </si>
   <si>
     <t>primary_image</t>
-  </si>
-  <si>
-    <t>Theremin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
-</t>
-  </si>
-  <si>
-    <t>לב טרמין היה פיזיקאי וממציא רוסי, שפעל בצומת שבין אלקטרוניקה, מוזיקה וטכנולוגיית חישה. חייו יוצאי הדופן כללו גם עבודה עבור שירותי המודיעין הסובייטיים ופיתוח טכנולוגיות האזנה.</t>
   </si>
   <si>
     <t>Natural Interaction / Musical Interaction</t>
@@ -1583,8 +1573,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P151" totalsRowShown="0" dataDxfId="16">
-  <autoFilter ref="A1:P151" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P150" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:P150" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F164D471-F0AB-430B-A6FB-6338D8DB3E2B}" name="id" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{F5ED8843-E467-4E3B-864E-7412714707BF}" name="era" dataDxfId="14"/>
@@ -1892,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1913,7 +1903,7 @@
     <col min="16" max="16" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1963,132 +1953,129 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>1928</v>
+        <v>1945</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="N2" s="3">
+        <v>119</v>
+      </c>
+      <c r="O2" s="3">
+        <v>162</v>
+      </c>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N3" s="3">
-        <v>119</v>
-      </c>
-      <c r="O3" s="3">
-        <v>162</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="3">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="3">
-        <v>35</v>
-      </c>
+      <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -2101,96 +2088,105 @@
         <v>38</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="3">
         <v>39</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="3">
+        <v>148</v>
+      </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="3">
-        <v>1955</v>
+        <v>1961</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="N6" s="3">
-        <v>39</v>
-      </c>
-      <c r="O6" s="3">
-        <v>148</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="3">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="N7" s="3">
+        <v>13</v>
+      </c>
+      <c r="O7" s="3">
         <v>122</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+      <c r="P7" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -2212,27 +2208,21 @@
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N8" s="3">
-        <v>13</v>
-      </c>
-      <c r="O8" s="3">
-        <v>122</v>
-      </c>
-      <c r="P8" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -2245,96 +2235,97 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="2" t="s">
         <v>52</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="3">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="3">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="N11" s="3">
+        <v>13</v>
+      </c>
+      <c r="O11" s="3">
+        <v>7</v>
+      </c>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -2347,31 +2338,27 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="L12" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N12" s="3">
+        <v>59</v>
+      </c>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>13</v>
-      </c>
-      <c r="O12" s="3">
-        <v>7</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" ht="171" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -2380,175 +2367,178 @@
         <v>1968</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>67</v>
+      </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
+        <v>11</v>
+      </c>
+      <c r="O13" s="3">
+        <v>7</v>
+      </c>
+      <c r="P13" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="3">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
-        <v>11</v>
-      </c>
-      <c r="O14" s="3">
-        <v>7</v>
-      </c>
-      <c r="P14" s="3">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="K14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N15" s="3"/>
+        <v>80</v>
+      </c>
+      <c r="N15" s="3">
+        <v>49</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3">
-        <v>1972</v>
+        <v>1989</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>83</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
       <c r="N16" s="3">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="C17" s="3">
-        <v>1989</v>
+        <v>1975</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>31</v>
-      </c>
+      <c r="K17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -2564,27 +2554,27 @@
         <v>90</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="3">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -2596,93 +2586,92 @@
       <c r="G19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="57" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N20" s="3"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3">
+        <v>144</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="57" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C21" s="3">
-        <v>1969</v>
+        <v>1981</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
+      <c r="L21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="N21" s="3">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" s="3">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>17</v>
@@ -2695,26 +2684,28 @@
         <v>99</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N22" s="3">
-        <v>121</v>
-      </c>
-      <c r="O22" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="O22" s="3">
+        <v>24</v>
+      </c>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C23" s="3">
         <v>1983</v>
@@ -2724,72 +2715,77 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>102</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="N23" s="3">
-        <v>21</v>
-      </c>
-      <c r="O23" s="3">
+        <v>139</v>
+      </c>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>24</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="N24" s="3">
-        <v>139</v>
-      </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="O24" s="3">
+        <v>22</v>
+      </c>
+      <c r="P24" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C25" s="3">
         <v>1984</v>
@@ -2804,34 +2800,28 @@
       <c r="G25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>110</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N25" s="3">
-        <v>21</v>
-      </c>
-      <c r="O25" s="3">
-        <v>22</v>
-      </c>
-      <c r="P25" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C26" s="3">
         <v>1984</v>
@@ -2841,98 +2831,95 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C27" s="3">
-        <v>1984</v>
+        <v>2001</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H27" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N27" s="3"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3">
+        <v>59</v>
+      </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C28" s="3">
-        <v>2001</v>
+        <v>1987</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3">
-        <v>59</v>
-      </c>
+      <c r="L28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
     <row r="29" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C29" s="3">
         <v>1987</v>
@@ -2942,140 +2929,140 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N29" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="N29" s="3">
+        <v>129</v>
+      </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C30" s="3">
-        <v>1987</v>
+        <v>2001</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H30" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
       <c r="N30" s="3">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
     <row r="31" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C31" s="3">
-        <v>2001</v>
+        <v>1989</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
+      <c r="K31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="N31" s="3">
-        <v>59</v>
-      </c>
-      <c r="O31" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="O31" s="3">
+        <v>71</v>
+      </c>
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C32" s="3">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>33</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N32" s="3">
-        <v>16</v>
-      </c>
-      <c r="O32" s="3">
-        <v>71</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="1:16" ht="114" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="C33" s="3">
         <v>1990</v>
@@ -3085,69 +3072,69 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C34" s="3">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="C35" s="3">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -3156,54 +3143,57 @@
       <c r="G35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N35" s="3"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3">
+        <v>3</v>
+      </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="C36" s="3">
-        <v>1949</v>
+        <v>1992</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3">
-        <v>3</v>
-      </c>
+      <c r="K36" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C37" s="3">
         <v>1992</v>
@@ -3218,31 +3208,28 @@
       <c r="G37" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="K37" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="L37" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C38" s="3">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>17</v>
@@ -3255,122 +3242,125 @@
         <v>156</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="57" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="C39" s="3">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N39" s="3"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3">
+        <v>5</v>
+      </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" ht="57" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C40" s="3">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K40" s="2"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3">
-        <v>5</v>
-      </c>
+      <c r="K40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C41" s="3">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="J41" s="2" t="s">
         <v>163</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C42" s="3">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>17</v>
@@ -3382,28 +3372,28 @@
       <c r="G42" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>166</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C43" s="3">
         <v>1995</v>
@@ -3422,62 +3412,62 @@
         <v>169</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N43" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="N43" s="3">
+        <v>129</v>
+      </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C44" s="3">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N44" s="3">
-        <v>129</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
     </row>
     <row r="45" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C45" s="3">
         <v>1996</v>
@@ -3487,12 +3477,9 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I45" s="2" t="s">
         <v>177</v>
       </c>
       <c r="K45" s="2" t="s">
@@ -3502,7 +3489,7 @@
         <v>178</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -3510,10 +3497,10 @@
     </row>
     <row r="46" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C46" s="3">
         <v>1996</v>
@@ -3528,28 +3515,31 @@
       <c r="G46" s="2" t="s">
         <v>180</v>
       </c>
+      <c r="H46" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="K46" s="2" t="s">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C47" s="3">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
@@ -3565,242 +3555,239 @@
         <v>184</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N47" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="N47" s="3">
+        <v>53</v>
+      </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C48" s="3">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>185</v>
+        <v>75</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="H48" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
       <c r="N48" s="3">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C49" s="3">
-        <v>2008</v>
+        <v>1997</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>78</v>
+        <v>187</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K49" s="2"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
+        <v>188</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="N49" s="3">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="C50" s="3">
-        <v>1997</v>
+        <v>1984</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>83</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
       <c r="N50" s="3">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C51" s="3">
-        <v>1984</v>
+        <v>1998</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="K51" s="2"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3">
-        <v>24</v>
-      </c>
+      <c r="L51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C52" s="3">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N52" s="3"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3">
+        <v>48</v>
+      </c>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
     </row>
-    <row r="53" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C53" s="3">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G53" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="K53" s="2"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3">
-        <v>48</v>
-      </c>
+      <c r="K53" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C54" s="3">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I54" s="2" t="s">
         <v>199</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>200</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -3808,10 +3795,10 @@
     </row>
     <row r="55" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C55" s="3">
         <v>1999</v>
@@ -3830,21 +3817,21 @@
         <v>203</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C56" s="3">
         <v>1999</v>
@@ -3860,92 +3847,107 @@
         <v>205</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>206</v>
+        <v>73</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C57" s="3">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K57" s="2" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N57" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="N57" s="3">
+        <v>141</v>
+      </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C58" s="3">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="2" t="s">
         <v>210</v>
       </c>
+      <c r="I58" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="K58" s="2" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="N58" s="3">
-        <v>141</v>
-      </c>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="O58" s="3">
+        <v>27</v>
+      </c>
+      <c r="P58" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C59" s="3">
         <v>2001</v>
@@ -3955,45 +3957,33 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>217</v>
+        <v>79</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N59" s="3">
-        <v>83</v>
-      </c>
-      <c r="O59" s="3">
-        <v>27</v>
-      </c>
-      <c r="P59" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C60" s="3">
         <v>2001</v>
@@ -4008,31 +3998,28 @@
       <c r="G60" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="K60" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="L60" s="3" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C61" s="3">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>17</v>
@@ -4045,24 +4032,24 @@
         <v>222</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C62" s="3">
         <v>2002</v>
@@ -4072,30 +4059,36 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="H62" s="2" t="s">
         <v>225</v>
       </c>
+      <c r="J62" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="K62" s="2" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C63" s="3">
         <v>2002</v>
@@ -4105,36 +4098,33 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C64" s="3">
         <v>2002</v>
@@ -4149,63 +4139,60 @@
       <c r="G64" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="K64" s="2" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N64" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="N64" s="3">
+        <v>141</v>
+      </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C65" s="3">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="K65" s="2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>145</v>
+        <v>73</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N65" s="3">
-        <v>141</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C66" s="3">
         <v>2003</v>
@@ -4215,65 +4202,65 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="K66" s="2" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N66" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="N66" s="3">
+        <v>141</v>
+      </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C67" s="3">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="K67" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N67" s="3">
-        <v>141</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C68" s="3">
         <v>2004</v>
@@ -4283,30 +4270,32 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G68" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="L68" s="3" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N68" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="N68" s="3">
+        <v>31</v>
+      </c>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C69" s="3">
         <v>2004</v>
@@ -4321,52 +4310,50 @@
       <c r="G69" s="2" t="s">
         <v>243</v>
       </c>
+      <c r="H69" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="K69" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N69" s="3">
-        <v>31</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C70" s="3">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="H70" s="2" t="s">
         <v>247</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
@@ -4374,10 +4361,10 @@
     </row>
     <row r="71" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C71" s="3">
         <v>2005</v>
@@ -4387,33 +4374,36 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="I71" s="2" t="s">
         <v>250</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C72" s="3">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>17</v>
@@ -4425,28 +4415,27 @@
       <c r="G72" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="K72" s="2" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N72" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="N72" s="3">
+        <v>124</v>
+      </c>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
     <row r="73" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C73" s="3">
         <v>2006</v>
@@ -4456,65 +4445,70 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="K73" s="2" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" s="3">
-        <v>124</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="N73" s="3"/>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C74" s="3">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="H74" s="2" t="s">
         <v>257</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>181</v>
+        <v>54</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="N74" s="3">
+        <v>142</v>
+      </c>
+      <c r="O74" s="3">
+        <v>120</v>
+      </c>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C75" s="3">
         <v>2007</v>
@@ -4529,113 +4523,102 @@
       <c r="G75" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="H75" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="K75" s="2" t="s">
-        <v>244</v>
+        <v>142</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="N75" s="3">
-        <v>142</v>
-      </c>
-      <c r="O75" s="3">
-        <v>120</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C76" s="3">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="K76" s="2" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N76" s="3">
-        <v>141</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C77" s="3">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N77" s="3"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>83</v>
+      </c>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C78" s="3">
         <v>2009</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="3"/>
@@ -4646,41 +4629,45 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C79" s="3">
         <v>2009</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K79" s="2"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3">
-        <v>83</v>
-      </c>
+      <c r="K79" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C80" s="3">
         <v>2009</v>
@@ -4690,30 +4677,39 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="I80" s="2" t="s">
         <v>270</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N80" s="3"/>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-    </row>
-    <row r="81" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="N80" s="3">
+        <v>59</v>
+      </c>
+      <c r="O80" s="3">
+        <v>80</v>
+      </c>
+      <c r="P80" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="C81" s="3">
         <v>2009</v>
@@ -4723,110 +4719,101 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G81" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>85</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N81" s="3">
-        <v>59</v>
-      </c>
-      <c r="O81" s="3">
-        <v>80</v>
-      </c>
-      <c r="P81" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>84</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="C82" s="3">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="H82" s="2" t="s">
         <v>278</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>279</v>
+        <v>19</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N82" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="N82" s="3">
+        <v>125</v>
+      </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
     <row r="83" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C83" s="3">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="K83" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="L83" s="3" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N83" s="3">
-        <v>125</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C84" s="3">
         <v>2011</v>
@@ -4845,21 +4832,21 @@
         <v>284</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C85" s="3">
         <v>2011</v>
@@ -4874,28 +4861,31 @@
       <c r="G85" s="2" t="s">
         <v>286</v>
       </c>
+      <c r="H85" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="K85" s="2" t="s">
-        <v>287</v>
+        <v>137</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C86" s="3">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>17</v>
@@ -4907,28 +4897,30 @@
       <c r="G86" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H86" s="2" t="s">
+      <c r="I86" s="2" t="s">
         <v>290</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N86" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="N86" s="3">
+        <v>135</v>
+      </c>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
     <row r="87" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C87" s="3">
         <v>2013</v>
@@ -4947,26 +4939,24 @@
         <v>293</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>173</v>
+        <v>276</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N87" s="3">
-        <v>135</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C88" s="3">
         <v>2013</v>
@@ -4981,28 +4971,25 @@
       <c r="G88" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="K88" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="L88" s="3" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C89" s="3">
         <v>2013</v>
@@ -5018,94 +5005,94 @@
         <v>298</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="N89" s="3">
+        <v>141</v>
+      </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
     <row r="90" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C90" s="3">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="K90" s="2" t="s">
-        <v>145</v>
+        <v>284</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="N90" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C91" s="3">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="K91" s="2" t="s">
-        <v>287</v>
+        <v>112</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" s="3">
-        <v>143</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C92" s="3">
         <v>2015</v>
@@ -5115,30 +5102,30 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="K92" s="2" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C93" s="3">
         <v>2015</v>
@@ -5148,30 +5135,32 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="K93" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N93" s="3"/>
+        <v>74</v>
+      </c>
+      <c r="N93" s="3">
+        <v>105</v>
+      </c>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C94" s="3">
         <v>2015</v>
@@ -5181,68 +5170,66 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="I94" s="2" t="s">
         <v>309</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N94" s="3">
-        <v>105</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C95" s="3">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I95" s="2" t="s">
         <v>312</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>313</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>313</v>
+        <v>65</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C96" s="3">
         <v>2016</v>
@@ -5257,25 +5244,28 @@
       <c r="G96" s="2" t="s">
         <v>315</v>
       </c>
+      <c r="J96" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="K96" s="2" t="s">
-        <v>316</v>
+        <v>65</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C97" s="3">
         <v>2016</v>
@@ -5290,50 +5280,47 @@
       <c r="G97" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="J97" s="2" t="s">
+      <c r="K97" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="K97" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="L97" s="3" t="s">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C98" s="3">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>323</v>
+        <v>112</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
@@ -5341,13 +5328,13 @@
     </row>
     <row r="99" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C99" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>17</v>
@@ -5360,13 +5347,13 @@
         <v>325</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>326</v>
+        <v>142</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
@@ -5374,118 +5361,118 @@
     </row>
     <row r="100" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C100" s="3">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="H100" s="2" t="s">
         <v>328</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N100" s="3"/>
-      <c r="O100" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="N100" s="3">
+        <v>26</v>
+      </c>
+      <c r="O100" s="3">
+        <v>128</v>
+      </c>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C101" s="3">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H101" s="2" t="s">
         <v>331</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>332</v>
+        <v>73</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="N101" s="3">
-        <v>26</v>
-      </c>
-      <c r="O101" s="3">
-        <v>128</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C102" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="K102" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N102" s="3">
-        <v>96</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C103" s="3">
         <v>2021</v>
@@ -5495,19 +5482,19 @@
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="K103" s="2" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>22</v>
+        <v>171</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
@@ -5515,13 +5502,13 @@
     </row>
     <row r="104" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="C104" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>17</v>
@@ -5533,25 +5520,30 @@
       <c r="G104" s="2" t="s">
         <v>338</v>
       </c>
+      <c r="I104" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="K104" s="2" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N104" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="N104" s="3">
+        <v>138</v>
+      </c>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C105" s="3">
         <v>2022</v>
@@ -5566,17 +5558,20 @@
       <c r="G105" s="2" t="s">
         <v>341</v>
       </c>
+      <c r="H105" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="I105" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>126</v>
+        <v>344</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N105" s="3">
         <v>138</v>
@@ -5584,53 +5579,45 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C106" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="I106" s="2" t="s">
         <v>346</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>347</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N106" s="3">
-        <v>138</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="N106" s="3"/>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C107" s="3">
         <v>2023</v>
@@ -5649,10 +5636,10 @@
         <v>350</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -5660,10 +5647,10 @@
     </row>
     <row r="108" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C108" s="3">
         <v>2023</v>
@@ -5682,21 +5669,23 @@
         <v>353</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N108" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="N108" s="3">
+        <v>138</v>
+      </c>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C109" s="3">
         <v>2023</v>
@@ -5712,13 +5701,13 @@
         <v>355</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N109" s="3">
         <v>138</v>
@@ -5726,34 +5715,34 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C110" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="K110" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N110" s="3">
         <v>138</v>
@@ -5761,12 +5750,12 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C111" s="3">
         <v>2024</v>
@@ -5776,19 +5765,19 @@
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="K111" s="2" t="s">
-        <v>356</v>
+        <v>123</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N111" s="3">
         <v>138</v>
@@ -5796,368 +5785,360 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C112" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="H112" s="2" t="s">
         <v>362</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>126</v>
+        <v>363</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N112" s="3">
-        <v>138</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N112" s="3"/>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="C113" s="3">
-        <v>2025</v>
+        <v>1945</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3" t="s">
-        <v>363</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F113" s="3"/>
       <c r="G113" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="K113" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="L113" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N113" s="3"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3">
+        <v>156</v>
+      </c>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C114" s="3">
-        <v>1945</v>
+        <v>2007</v>
       </c>
       <c r="D114" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C115" s="3">
-        <v>2007</v>
+        <v>1973</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C116" s="3">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F116" s="3"/>
+      <c r="G116" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3">
-        <v>21</v>
-      </c>
-      <c r="O116" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="O116" s="3">
+        <v>129</v>
+      </c>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C117" s="3">
-        <v>1969</v>
+        <v>2006</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="2" t="s">
-        <v>375</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3">
-        <v>13</v>
-      </c>
-      <c r="O117" s="3">
-        <v>129</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O117" s="3"/>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C118" s="3">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H118" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="G118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
     <row r="119" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C119" s="3">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E119" s="3"/>
+        <v>364</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>377</v>
+      </c>
       <c r="F119" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="H119" s="2" t="s">
         <v>379</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3">
-        <v>85</v>
-      </c>
-      <c r="O119" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="O119" s="3">
+        <v>146</v>
+      </c>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="C120" s="3">
-        <v>1986</v>
+        <v>2011</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E120" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3">
-        <v>144</v>
-      </c>
-      <c r="O120" s="3">
-        <v>146</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>275</v>
+        <v>134</v>
       </c>
       <c r="C121" s="3">
-        <v>2011</v>
+        <v>1991</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3" t="s">
-        <v>329</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F121" s="3"/>
       <c r="G121" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3">
-        <v>104</v>
-      </c>
-      <c r="O121" s="3"/>
-      <c r="P121" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="O121" s="3">
+        <v>29</v>
+      </c>
+      <c r="P121" s="3">
+        <v>44</v>
+      </c>
     </row>
     <row r="122" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C122" s="3">
         <v>1991</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-      <c r="N122" s="3">
-        <v>2</v>
-      </c>
-      <c r="O122" s="3">
-        <v>29</v>
-      </c>
-      <c r="P122" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+      <c r="P122" s="3"/>
+    </row>
+    <row r="123" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>137</v>
+        <v>272</v>
       </c>
       <c r="C123" s="3">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="3"/>
@@ -6166,25 +6147,25 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C124" s="3">
-        <v>2010</v>
+        <v>1965</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="3"/>
@@ -6193,165 +6174,174 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="C125" s="3">
-        <v>1965</v>
+        <v>2020</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
-      <c r="O125" s="3"/>
-      <c r="P125" s="3"/>
-    </row>
-    <row r="126" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N125" s="3">
+        <v>89</v>
+      </c>
+      <c r="O125" s="3">
+        <v>105</v>
+      </c>
+      <c r="P125" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C126" s="3">
-        <v>2020</v>
+        <v>1929</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
-      <c r="N126" s="3">
-        <v>89</v>
-      </c>
-      <c r="O126" s="3">
-        <v>105</v>
-      </c>
-      <c r="P126" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="P126" s="3"/>
+    </row>
+    <row r="127" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="C127" s="3">
-        <v>1929</v>
+        <v>2022</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>367</v>
+        <v>66</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
-      <c r="O127" s="3"/>
+      <c r="N127" s="3">
+        <v>108</v>
+      </c>
+      <c r="O127" s="3">
+        <v>109</v>
+      </c>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="C128" s="3">
-        <v>2022</v>
+        <v>1983</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3">
-        <v>108</v>
-      </c>
-      <c r="O128" s="3">
-        <v>109</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O128" s="3"/>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="C129" s="3">
-        <v>1983</v>
+        <v>1997</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>399</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3">
-        <v>23</v>
-      </c>
-      <c r="O129" s="3"/>
-      <c r="P129" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="O129" s="3">
+        <v>50</v>
+      </c>
+      <c r="P129" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="130" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C130" s="3">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>400</v>
@@ -6359,342 +6349,338 @@
       <c r="F130" s="3"/>
       <c r="G130" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3">
-        <v>55</v>
-      </c>
-      <c r="O130" s="3">
-        <v>50</v>
-      </c>
-      <c r="P130" s="3">
-        <v>58</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="O130" s="3"/>
+      <c r="P130" s="3"/>
     </row>
     <row r="131" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="C131" s="3">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="O131" s="3"/>
       <c r="P131" s="3"/>
     </row>
-    <row r="132" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="C132" s="3">
-        <v>2014</v>
+        <v>1986</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="G132" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F132" s="3"/>
-      <c r="G132" s="2" t="s">
+      <c r="I132" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="K132" s="2"/>
-      <c r="L132" s="3"/>
-      <c r="M132" s="3"/>
+      <c r="K132" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L132" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="N132" s="3">
-        <v>93</v>
-      </c>
-      <c r="O132" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="O132" s="3">
+        <v>20</v>
+      </c>
       <c r="P132" s="3"/>
     </row>
-    <row r="133" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C133" s="3">
-        <v>1986</v>
+        <v>2001</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="K133" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="L133" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="I133" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="M133" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N133" s="3">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="O133" s="3">
-        <v>20</v>
-      </c>
-      <c r="P133" s="3"/>
-    </row>
-    <row r="134" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="P133" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C134" s="3">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E134" s="3"/>
-      <c r="F134" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E134" s="3" t="s">
         <v>412</v>
       </c>
+      <c r="F134" s="3"/>
       <c r="G134" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="I134" s="2" t="s">
+      <c r="K134" s="2"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3">
+        <v>127</v>
+      </c>
+      <c r="O134" s="3">
+        <v>145</v>
+      </c>
+      <c r="P134" s="3"/>
+    </row>
+    <row r="135" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
+        <v>147</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C135" s="3">
+        <v>2001</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="M134" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N134" s="3">
-        <v>146</v>
-      </c>
-      <c r="O134" s="3">
-        <v>147</v>
-      </c>
-      <c r="P134" s="3">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>146</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C135" s="3">
-        <v>2011</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3">
-        <v>127</v>
-      </c>
-      <c r="O135" s="3">
         <v>145</v>
       </c>
+      <c r="O135" s="3"/>
       <c r="P135" s="3"/>
     </row>
-    <row r="136" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C136" s="3">
-        <v>2001</v>
+        <v>1947</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3">
-        <v>145</v>
-      </c>
-      <c r="O136" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="O136" s="3">
+        <v>150</v>
+      </c>
       <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C137" s="3">
-        <v>1947</v>
+        <v>1969</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E137" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G137" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F137" s="3"/>
-      <c r="G137" s="2" t="s">
+      <c r="I137" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="K137" s="2"/>
-      <c r="L137" s="3"/>
-      <c r="M137" s="3"/>
+      <c r="J137" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="N137" s="3">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="O137" s="3">
+        <v>153</v>
+      </c>
+      <c r="P137" s="3"/>
+    </row>
+    <row r="138" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
         <v>150</v>
-      </c>
-      <c r="P137" s="3"/>
-    </row>
-    <row r="138" spans="1:16" ht="114" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C138" s="3">
-        <v>1969</v>
+        <v>1957</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>422</v>
+      </c>
       <c r="F138" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="J138" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="K138" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="K138" s="2"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3"/>
       <c r="N138" s="3">
         <v>148</v>
       </c>
       <c r="O138" s="3">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P138" s="3"/>
     </row>
-    <row r="139" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="3">
-        <v>1957</v>
+        <v>1978</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="3"/>
+      <c r="G139" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="G139" s="2" t="s">
+      <c r="J139" s="2" t="s">
         <v>427</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3">
-        <v>148</v>
-      </c>
-      <c r="O139" s="3">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C140" s="3">
-        <v>1978</v>
+        <v>2008</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>428</v>
@@ -6703,184 +6689,179 @@
       <c r="G140" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="J140" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
-      <c r="N140" s="3">
-        <v>150</v>
-      </c>
+      <c r="N140" s="3"/>
       <c r="O140" s="3"/>
       <c r="P140" s="3"/>
     </row>
-    <row r="141" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C141" s="3">
-        <v>2008</v>
+        <v>1969</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-      <c r="O141" s="3"/>
-      <c r="P141" s="3"/>
-    </row>
-    <row r="142" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="N141" s="3">
+        <v>149</v>
+      </c>
+      <c r="O141" s="3">
+        <v>150</v>
+      </c>
+      <c r="P141" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="C142" s="3">
-        <v>1969</v>
+        <v>2003</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3">
-        <v>149</v>
-      </c>
-      <c r="O142" s="3">
-        <v>150</v>
-      </c>
-      <c r="P142" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+    </row>
+    <row r="143" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C143" s="3">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>367</v>
+        <v>66</v>
       </c>
       <c r="E143" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="F143" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F143" s="3"/>
       <c r="G143" s="2" t="s">
         <v>436</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
-      <c r="N143" s="3">
-        <v>145</v>
-      </c>
+      <c r="N143" s="3"/>
       <c r="O143" s="3"/>
       <c r="P143" s="3"/>
     </row>
-    <row r="144" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="C144" s="3">
-        <v>2000</v>
+        <v>1945</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>69</v>
+        <v>364</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="F144" s="3"/>
+      <c r="G144" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
-      <c r="N144" s="3"/>
+      <c r="N144" s="3">
+        <v>119</v>
+      </c>
       <c r="O144" s="3"/>
       <c r="P144" s="3"/>
     </row>
     <row r="145" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="C145" s="3">
-        <v>1945</v>
+        <v>2022</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
-      <c r="N145" s="3">
-        <v>119</v>
-      </c>
+      <c r="N145" s="3"/>
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="C146" s="3">
-        <v>2022</v>
+        <v>1973</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="3"/>
@@ -6889,25 +6870,25 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c r="C147" s="3">
-        <v>1973</v>
+        <v>2021</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="3"/>
@@ -6918,126 +6899,99 @@
     </row>
     <row r="148" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C148" s="3">
-        <v>2021</v>
+        <v>1972</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="G148" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F148" s="3"/>
-      <c r="G148" s="2" t="s">
+      <c r="J148" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="K148" s="2"/>
-      <c r="L148" s="3"/>
-      <c r="M148" s="3"/>
-      <c r="N148" s="3"/>
+      <c r="K148" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M148" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N148" s="3">
+        <v>161</v>
+      </c>
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C149" s="3">
-        <v>1972</v>
+        <v>1986</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>448</v>
       </c>
+      <c r="F149" s="3"/>
       <c r="G149" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J149" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="M149" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="K149" s="2"/>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
       <c r="N149" s="3">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C150" s="3">
-        <v>1986</v>
+        <v>1945</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="F150" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="G150" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
-    </row>
-    <row r="151" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
-        <v>162</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" s="3">
-        <v>1945</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="K151" s="2"/>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3">
-        <v>2</v>
-      </c>
-      <c r="O151" s="3"/>
-      <c r="P151" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F2A04-0B28-4781-B7D1-2E760D2A3345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D42100-E05C-4A01-B857-894301C1BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="454">
   <si>
     <t>id</t>
   </si>
@@ -74,6 +74,16 @@
   </si>
   <si>
     <t>primary_image</t>
+  </si>
+  <si>
+    <t>Theremin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
+</t>
+  </si>
+  <si>
+    <t>לב טרמין היה פיזיקאי וממציא רוסי, שפעל בצומת שבין אלקטרוניקה, מוזיקה וטכנולוגיית חישה. חייו יוצאי הדופן כללו גם עבודה עבור שירותי המודיעין הסובייטיים ופיתוח טכנולוגיות האזנה.</t>
   </si>
   <si>
     <t>Natural Interaction / Musical Interaction</t>
@@ -1573,8 +1583,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P150" totalsRowShown="0" dataDxfId="16">
-  <autoFilter ref="A1:P150" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P151" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:P151" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F164D471-F0AB-430B-A6FB-6338D8DB3E2B}" name="id" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{F5ED8843-E467-4E3B-864E-7412714707BF}" name="era" dataDxfId="14"/>
@@ -1882,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1903,7 +1913,7 @@
     <col min="16" max="16" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1953,129 +1963,132 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C2" s="3">
-        <v>1945</v>
+        <v>1928</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="3">
-        <v>119</v>
-      </c>
-      <c r="O2" s="3">
-        <v>162</v>
-      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
       <c r="P2" s="3"/>
     </row>
-    <row r="3" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="3">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="N3" s="3">
-        <v>35</v>
-      </c>
-      <c r="O3" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="O3" s="3">
+        <v>162</v>
+      </c>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="3">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="3"/>
+      <c r="N4" s="3">
+        <v>35</v>
+      </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="3">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>17</v>
@@ -2088,105 +2101,96 @@
         <v>38</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N5" s="3">
-        <v>39</v>
-      </c>
-      <c r="O5" s="3">
-        <v>148</v>
-      </c>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="3">
-        <v>1961</v>
+        <v>1955</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="L6" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="N6" s="3">
-        <v>122</v>
-      </c>
-      <c r="O6" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="O6" s="3">
+        <v>148</v>
+      </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="3">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="N7" s="3">
-        <v>13</v>
-      </c>
-      <c r="O7" s="3">
         <v>122</v>
       </c>
-      <c r="P7" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -2208,21 +2212,27 @@
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="N8" s="3">
+        <v>13</v>
+      </c>
+      <c r="O8" s="3">
+        <v>122</v>
+      </c>
+      <c r="P8" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -2235,97 +2245,96 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>52</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="3">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="L10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="3">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="L11" s="3" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="3">
-        <v>13</v>
-      </c>
-      <c r="O11" s="3">
-        <v>7</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -2338,27 +2347,31 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="N12" s="3">
+        <v>13</v>
+      </c>
+      <c r="O12" s="3">
+        <v>7</v>
+      </c>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -2367,178 +2380,175 @@
         <v>1968</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3">
-        <v>11</v>
-      </c>
-      <c r="O13" s="3">
-        <v>7</v>
-      </c>
-      <c r="P13" s="3">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="M13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="3">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="F14" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="K14" s="2"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
+        <v>11</v>
+      </c>
+      <c r="O14" s="3">
+        <v>7</v>
+      </c>
+      <c r="P14" s="3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="L15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N15" s="3">
-        <v>49</v>
-      </c>
+      <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="C16" s="3">
-        <v>1989</v>
+        <v>1972</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
       <c r="N16" s="3">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="3"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
+        <v>31</v>
+      </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
     <row r="18" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="3">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -2554,27 +2564,27 @@
         <v>90</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="3">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -2586,92 +2596,93 @@
       <c r="G19" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="K19" s="2" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="57" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="3">
-        <v>1969</v>
+        <v>1979</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>144</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="57" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3">
-        <v>1981</v>
+        <v>1969</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="K21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
       <c r="N21" s="3">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22" s="3">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>17</v>
@@ -2684,28 +2695,26 @@
         <v>99</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N22" s="3">
-        <v>21</v>
-      </c>
-      <c r="O22" s="3">
-        <v>24</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
-    <row r="23" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C23" s="3">
         <v>1983</v>
@@ -2715,77 +2724,72 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="L23" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="N23" s="3">
-        <v>139</v>
-      </c>
-      <c r="O23" s="3"/>
+        <v>21</v>
+      </c>
+      <c r="O23" s="3">
+        <v>24</v>
+      </c>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" s="3">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="L24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="N24" s="3">
-        <v>21</v>
-      </c>
-      <c r="O24" s="3">
-        <v>22</v>
-      </c>
-      <c r="P24" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C25" s="3">
         <v>1984</v>
@@ -2800,28 +2804,34 @@
       <c r="G25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>110</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+      <c r="N25" s="3">
+        <v>21</v>
+      </c>
+      <c r="O25" s="3">
+        <v>22</v>
+      </c>
+      <c r="P25" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C26" s="3">
         <v>1984</v>
@@ -2831,95 +2841,98 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C27" s="3">
-        <v>2001</v>
+        <v>1984</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3">
-        <v>59</v>
-      </c>
+      <c r="K27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C28" s="3">
-        <v>1987</v>
+        <v>2001</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="K28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="L28" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3">
+        <v>59</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
     <row r="29" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3">
         <v>1987</v>
@@ -2929,140 +2942,140 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="L29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N29" s="3">
-        <v>129</v>
-      </c>
+      <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C30" s="3">
-        <v>2001</v>
+        <v>1987</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K30" s="2"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
+      <c r="J30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="N30" s="3">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
     <row r="31" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C31" s="3">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H31" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
       <c r="N31" s="3">
-        <v>16</v>
-      </c>
-      <c r="O31" s="3">
-        <v>71</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C32" s="3">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>136</v>
       </c>
       <c r="K32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N32" s="3">
+        <v>16</v>
+      </c>
+      <c r="O32" s="3">
+        <v>71</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>33</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C33" s="3">
         <v>1990</v>
@@ -3072,69 +3085,69 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="M33" s="3" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C34" s="3">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K34" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="L34" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C35" s="3">
-        <v>1949</v>
+        <v>1991</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
@@ -3143,57 +3156,54 @@
       <c r="G35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3">
-        <v>3</v>
-      </c>
+      <c r="K35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="C36" s="3">
-        <v>1992</v>
+        <v>1949</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N36" s="3"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3">
+        <v>3</v>
+      </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C37" s="3">
         <v>1992</v>
@@ -3208,28 +3218,31 @@
       <c r="G37" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="H37" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="K37" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C38" s="3">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>17</v>
@@ -3242,125 +3255,122 @@
         <v>156</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" ht="57" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="C39" s="3">
-        <v>1985</v>
+        <v>1993</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K39" s="2"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3">
-        <v>5</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="57" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C40" s="3">
-        <v>1993</v>
+        <v>1985</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N40" s="3"/>
+        <v>161</v>
+      </c>
+      <c r="K40" s="2"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3">
+        <v>5</v>
+      </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C41" s="3">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="J41" s="2" t="s">
         <v>163</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C42" s="3">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>17</v>
@@ -3372,28 +3382,28 @@
       <c r="G42" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>166</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C43" s="3">
         <v>1995</v>
@@ -3412,62 +3422,62 @@
         <v>169</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N43" s="3">
-        <v>129</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C44" s="3">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="L44" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="M44" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="N44" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N44" s="3">
+        <v>129</v>
+      </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
     </row>
     <row r="45" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C45" s="3">
         <v>1996</v>
@@ -3477,9 +3487,12 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>177</v>
       </c>
       <c r="K45" s="2" t="s">
@@ -3489,7 +3502,7 @@
         <v>178</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -3497,10 +3510,10 @@
     </row>
     <row r="46" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C46" s="3">
         <v>1996</v>
@@ -3515,31 +3528,28 @@
       <c r="G46" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="L46" s="3" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
     </row>
-    <row r="47" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C47" s="3">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
@@ -3555,239 +3565,242 @@
         <v>184</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N47" s="3">
-        <v>53</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C48" s="3">
-        <v>2008</v>
+        <v>1997</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K48" s="2"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
+      <c r="H48" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N48" s="3">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
     </row>
-    <row r="49" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C49" s="3">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="K49" s="2"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
       <c r="N49" s="3">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
     </row>
-    <row r="50" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="C50" s="3">
-        <v>1984</v>
+        <v>1997</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="K50" s="2"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
+        <v>191</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="N50" s="3">
-        <v>24</v>
+        <v>141</v>
       </c>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C51" s="3">
-        <v>1998</v>
+        <v>1984</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K51" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N51" s="3"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3">
+        <v>24</v>
+      </c>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C52" s="3">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K52" s="2"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3">
-        <v>48</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
     </row>
-    <row r="53" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C53" s="3">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I53" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="N53" s="3"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3">
+        <v>48</v>
+      </c>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
     </row>
-    <row r="54" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C54" s="3">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="I54" s="2" t="s">
         <v>199</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>200</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -3795,10 +3808,10 @@
     </row>
     <row r="55" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C55" s="3">
         <v>1999</v>
@@ -3817,21 +3830,21 @@
         <v>203</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
     </row>
-    <row r="56" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C56" s="3">
         <v>1999</v>
@@ -3847,107 +3860,92 @@
         <v>205</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C57" s="3">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N57" s="3">
-        <v>141</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N57" s="3"/>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C58" s="3">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H58" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="K58" s="2" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>214</v>
+        <v>145</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="N58" s="3">
-        <v>83</v>
-      </c>
-      <c r="O58" s="3">
-        <v>27</v>
-      </c>
-      <c r="P58" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C59" s="3">
         <v>2001</v>
@@ -3957,33 +3955,45 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J59" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="L59" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="M59" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="N59" s="3">
+        <v>83</v>
+      </c>
+      <c r="O59" s="3">
+        <v>27</v>
+      </c>
+      <c r="P59" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C60" s="3">
         <v>2001</v>
@@ -3998,28 +4008,31 @@
       <c r="G60" s="2" t="s">
         <v>219</v>
       </c>
+      <c r="I60" s="2" t="s">
+        <v>220</v>
+      </c>
       <c r="K60" s="2" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
     </row>
-    <row r="61" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C61" s="3">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>17</v>
@@ -4032,24 +4045,24 @@
         <v>222</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
       <c r="P61" s="3"/>
     </row>
-    <row r="62" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C62" s="3">
         <v>2002</v>
@@ -4059,36 +4072,30 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H62" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="J62" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="K62" s="2" t="s">
-        <v>227</v>
+        <v>140</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
     </row>
-    <row r="63" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C63" s="3">
         <v>2002</v>
@@ -4098,33 +4105,36 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="L63" s="3" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
     </row>
-    <row r="64" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C64" s="3">
         <v>2002</v>
@@ -4139,60 +4149,63 @@
       <c r="G64" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="H64" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="K64" s="2" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N64" s="3">
-        <v>141</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N64" s="3"/>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
     </row>
-    <row r="65" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C65" s="3">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N65" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="N65" s="3">
+        <v>141</v>
+      </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
     </row>
-    <row r="66" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C66" s="3">
         <v>2003</v>
@@ -4202,65 +4215,65 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N66" s="3">
-        <v>141</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C67" s="3">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N67" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="N67" s="3">
+        <v>141</v>
+      </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C68" s="3">
         <v>2004</v>
@@ -4270,32 +4283,30 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N68" s="3">
-        <v>31</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
     </row>
-    <row r="69" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C69" s="3">
         <v>2004</v>
@@ -4310,50 +4321,52 @@
       <c r="G69" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="L69" s="3" t="s">
-        <v>142</v>
+        <v>57</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N69" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="N69" s="3">
+        <v>31</v>
+      </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C70" s="3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>247</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
@@ -4361,10 +4374,10 @@
     </row>
     <row r="71" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C71" s="3">
         <v>2005</v>
@@ -4374,36 +4387,33 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I71" s="2" t="s">
         <v>250</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C72" s="3">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>17</v>
@@ -4415,27 +4425,28 @@
       <c r="G72" s="2" t="s">
         <v>252</v>
       </c>
+      <c r="I72" s="2" t="s">
+        <v>253</v>
+      </c>
       <c r="K72" s="2" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N72" s="3">
-        <v>124</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
     <row r="73" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C73" s="3">
         <v>2006</v>
@@ -4445,70 +4456,65 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N73" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N73" s="3">
+        <v>124</v>
+      </c>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C74" s="3">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="H74" s="2" t="s">
         <v>257</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N74" s="3">
-        <v>142</v>
-      </c>
-      <c r="O74" s="3">
+        <v>58</v>
+      </c>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <v>77</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>78</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="C75" s="3">
         <v>2007</v>
@@ -4523,102 +4529,113 @@
       <c r="G75" s="2" t="s">
         <v>259</v>
       </c>
+      <c r="H75" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="K75" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N75" s="3">
         <v>142</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N75" s="3">
-        <v>141</v>
-      </c>
-      <c r="O75" s="3"/>
+      <c r="O75" s="3">
+        <v>120</v>
+      </c>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C76" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N76" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="N76" s="3">
+        <v>141</v>
+      </c>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C77" s="3">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3">
-        <v>83</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N77" s="3"/>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C78" s="3">
         <v>2009</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="3"/>
@@ -4629,45 +4646,41 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C79" s="3">
         <v>2009</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N79" s="3"/>
+        <v>268</v>
+      </c>
+      <c r="K79" s="2"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>83</v>
+      </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C80" s="3">
         <v>2009</v>
@@ -4677,39 +4690,30 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I80" s="2" t="s">
         <v>270</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>271</v>
+        <v>114</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N80" s="3">
-        <v>59</v>
-      </c>
-      <c r="O80" s="3">
-        <v>80</v>
-      </c>
-      <c r="P80" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>272</v>
+        <v>120</v>
       </c>
       <c r="C81" s="3">
         <v>2009</v>
@@ -4719,101 +4723,110 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="I81" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="L81" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N81" s="3">
+        <v>59</v>
+      </c>
+      <c r="O81" s="3">
+        <v>80</v>
+      </c>
+      <c r="P81" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <v>84</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="K81" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>85</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="C82" s="3">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="H82" s="2" t="s">
         <v>278</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>19</v>
+        <v>279</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N82" s="3">
-        <v>125</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
     <row r="83" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C83" s="3">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>281</v>
+        <v>22</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N83" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N83" s="3">
+        <v>125</v>
+      </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C84" s="3">
         <v>2011</v>
@@ -4832,21 +4845,21 @@
         <v>284</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C85" s="3">
         <v>2011</v>
@@ -4861,31 +4874,28 @@
       <c r="G85" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="L85" s="3" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C86" s="3">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>17</v>
@@ -4897,30 +4907,28 @@
       <c r="G86" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="I86" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>290</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N86" s="3">
-        <v>135</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
     <row r="87" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C87" s="3">
         <v>2013</v>
@@ -4939,24 +4947,26 @@
         <v>293</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>276</v>
+        <v>173</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N87" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N87" s="3">
+        <v>135</v>
+      </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C88" s="3">
         <v>2013</v>
@@ -4971,25 +4981,28 @@
       <c r="G88" s="2" t="s">
         <v>295</v>
       </c>
+      <c r="I88" s="2" t="s">
+        <v>296</v>
+      </c>
       <c r="K88" s="2" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>20</v>
+        <v>116</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C89" s="3">
         <v>2013</v>
@@ -5005,94 +5018,94 @@
         <v>298</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>142</v>
+        <v>299</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N89" s="3">
-        <v>141</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N89" s="3"/>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
     <row r="90" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C90" s="3">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>284</v>
+        <v>145</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="N90" s="3">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C91" s="3">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>112</v>
+        <v>287</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N91" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N91" s="3">
+        <v>143</v>
+      </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C92" s="3">
         <v>2015</v>
@@ -5102,30 +5115,30 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C93" s="3">
         <v>2015</v>
@@ -5135,32 +5148,30 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N93" s="3">
-        <v>105</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C94" s="3">
         <v>2015</v>
@@ -5170,66 +5181,68 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="I94" s="2" t="s">
         <v>309</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>310</v>
+        <v>76</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N94" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N94" s="3">
+        <v>105</v>
+      </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C95" s="3">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="I95" s="2" t="s">
         <v>312</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>313</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>65</v>
+        <v>313</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C96" s="3">
         <v>2016</v>
@@ -5244,28 +5257,25 @@
       <c r="G96" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="J96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="L96" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C97" s="3">
         <v>2016</v>
@@ -5280,47 +5290,50 @@
       <c r="G97" s="2" t="s">
         <v>318</v>
       </c>
+      <c r="J97" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="K97" s="2" t="s">
-        <v>319</v>
+        <v>68</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>320</v>
+        <v>68</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C98" s="3">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="K98" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="M98" s="3" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
@@ -5328,13 +5341,13 @@
     </row>
     <row r="99" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C99" s="3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>17</v>
@@ -5347,13 +5360,13 @@
         <v>325</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
@@ -5361,118 +5374,118 @@
     </row>
     <row r="100" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C100" s="3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H100" s="2" t="s">
         <v>328</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>329</v>
+        <v>145</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N100" s="3">
-        <v>26</v>
-      </c>
-      <c r="O100" s="3">
-        <v>128</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C101" s="3">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="2" t="s">
         <v>331</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>73</v>
+        <v>332</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="N101" s="3">
-        <v>96</v>
-      </c>
-      <c r="O101" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="O101" s="3">
+        <v>128</v>
+      </c>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C102" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N102" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N102" s="3">
+        <v>96</v>
+      </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C103" s="3">
         <v>2021</v>
@@ -5482,19 +5495,19 @@
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>171</v>
+        <v>22</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
@@ -5502,13 +5515,13 @@
     </row>
     <row r="104" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>336</v>
+        <v>275</v>
       </c>
       <c r="C104" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>17</v>
@@ -5520,30 +5533,25 @@
       <c r="G104" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="K104" s="2" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="N104" s="3">
-        <v>138</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N104" s="3"/>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C105" s="3">
         <v>2022</v>
@@ -5558,20 +5566,17 @@
       <c r="G105" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="H105" s="2" t="s">
+      <c r="I105" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="K105" s="2" t="s">
-        <v>344</v>
+        <v>126</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N105" s="3">
         <v>138</v>
@@ -5579,45 +5584,53 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C106" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>346</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>347</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N106" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="N106" s="3">
+        <v>138</v>
+      </c>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C107" s="3">
         <v>2023</v>
@@ -5636,10 +5649,10 @@
         <v>350</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -5647,10 +5660,10 @@
     </row>
     <row r="108" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C108" s="3">
         <v>2023</v>
@@ -5669,23 +5682,21 @@
         <v>353</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="N108" s="3">
-        <v>138</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N108" s="3"/>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C109" s="3">
         <v>2023</v>
@@ -5701,13 +5712,13 @@
         <v>355</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N109" s="3">
         <v>138</v>
@@ -5715,34 +5726,34 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C110" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K110" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="L110" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N110" s="3">
         <v>138</v>
@@ -5750,12 +5761,12 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C111" s="3">
         <v>2024</v>
@@ -5765,19 +5776,19 @@
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>123</v>
+        <v>356</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N111" s="3">
         <v>138</v>
@@ -5785,360 +5796,368 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C112" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="H112" s="2" t="s">
         <v>362</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>363</v>
+        <v>126</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N112" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="N112" s="3">
+        <v>138</v>
+      </c>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="C113" s="3">
-        <v>1945</v>
+        <v>2025</v>
       </c>
       <c r="D113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="H113" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="2" t="s">
+      <c r="K113" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="K113" s="2"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3">
-        <v>156</v>
-      </c>
+      <c r="L113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N113" s="3"/>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C114" s="3">
-        <v>2007</v>
+        <v>1945</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3" t="s">
         <v>367</v>
       </c>
+      <c r="E114" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F114" s="3"/>
       <c r="G114" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C115" s="3">
-        <v>1973</v>
+        <v>2007</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C116" s="3">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F116" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G116" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3">
-        <v>13</v>
-      </c>
-      <c r="O116" s="3">
-        <v>129</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="O116" s="3"/>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C117" s="3">
-        <v>2006</v>
+        <v>1969</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G117" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="K117" s="2"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3">
-        <v>75</v>
-      </c>
-      <c r="O117" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="O117" s="3">
+        <v>129</v>
+      </c>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C118" s="3">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="H118" s="2" t="s">
         <v>376</v>
       </c>
+      <c r="G118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
     <row r="119" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C119" s="3">
-        <v>1986</v>
+        <v>2003</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E119" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="G119" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="H119" s="2" t="s">
         <v>379</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3">
-        <v>144</v>
-      </c>
-      <c r="O119" s="3">
-        <v>146</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="O119" s="3"/>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="C120" s="3">
-        <v>2011</v>
+        <v>1986</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E120" s="3"/>
+        <v>367</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="F120" s="3" t="s">
-        <v>326</v>
+        <v>381</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3">
-        <v>104</v>
-      </c>
-      <c r="O120" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="O120" s="3">
+        <v>146</v>
+      </c>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>134</v>
+        <v>275</v>
       </c>
       <c r="C121" s="3">
-        <v>1991</v>
+        <v>2011</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F121" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G121" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3">
-        <v>2</v>
-      </c>
-      <c r="O121" s="3">
-        <v>29</v>
-      </c>
-      <c r="P121" s="3">
-        <v>44</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O121" s="3"/>
+      <c r="P121" s="3"/>
     </row>
     <row r="122" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C122" s="3">
         <v>1991</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>364</v>
+        <v>69</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
-      <c r="O122" s="3"/>
-      <c r="P122" s="3"/>
-    </row>
-    <row r="123" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+      <c r="N122" s="3">
+        <v>2</v>
+      </c>
+      <c r="O122" s="3">
+        <v>29</v>
+      </c>
+      <c r="P122" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>272</v>
+        <v>137</v>
       </c>
       <c r="C123" s="3">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="3"/>
@@ -6147,25 +6166,25 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C124" s="3">
-        <v>1965</v>
+        <v>2010</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="3"/>
@@ -6174,174 +6193,165 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c r="C125" s="3">
-        <v>2020</v>
+        <v>1965</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
-      <c r="N125" s="3">
-        <v>89</v>
-      </c>
-      <c r="O125" s="3">
-        <v>105</v>
-      </c>
-      <c r="P125" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+    </row>
+    <row r="126" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C126" s="3">
-        <v>1929</v>
+        <v>2020</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-      <c r="O126" s="3"/>
-      <c r="P126" s="3"/>
-    </row>
-    <row r="127" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N126" s="3">
+        <v>89</v>
+      </c>
+      <c r="O126" s="3">
+        <v>105</v>
+      </c>
+      <c r="P126" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>336</v>
+        <v>16</v>
       </c>
       <c r="C127" s="3">
-        <v>2022</v>
+        <v>1929</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>66</v>
+        <v>367</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
-      <c r="N127" s="3">
-        <v>108</v>
-      </c>
-      <c r="O127" s="3">
-        <v>109</v>
-      </c>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="C128" s="3">
-        <v>1983</v>
+        <v>2022</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3">
-        <v>23</v>
-      </c>
-      <c r="O128" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="O128" s="3">
+        <v>109</v>
+      </c>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C129" s="3">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="H129" s="2" t="s">
         <v>399</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3">
-        <v>55</v>
-      </c>
-      <c r="O129" s="3">
-        <v>50</v>
-      </c>
-      <c r="P129" s="3">
-        <v>58</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O129" s="3"/>
+      <c r="P129" s="3"/>
     </row>
     <row r="130" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C130" s="3">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>400</v>
@@ -6349,338 +6359,342 @@
       <c r="F130" s="3"/>
       <c r="G130" s="2" t="s">
         <v>401</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3">
-        <v>77</v>
-      </c>
-      <c r="O130" s="3"/>
-      <c r="P130" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="O130" s="3">
+        <v>50</v>
+      </c>
+      <c r="P130" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="131" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>272</v>
+        <v>120</v>
       </c>
       <c r="C131" s="3">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="O131" s="3"/>
       <c r="P131" s="3"/>
     </row>
-    <row r="132" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
+        <v>143</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2014</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F132" s="3"/>
+      <c r="G132" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K132" s="2"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3">
+        <v>93</v>
+      </c>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3"/>
+    </row>
+    <row r="133" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
         <v>144</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C132" s="3">
+      <c r="B133" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C133" s="3">
         <v>1986</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="M132" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N132" s="3">
-        <v>127</v>
-      </c>
-      <c r="O132" s="3">
-        <v>20</v>
-      </c>
-      <c r="P132" s="3"/>
-    </row>
-    <row r="133" spans="1:16" ht="171" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>145</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C133" s="3">
-        <v>2001</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I133" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="L133" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="K133" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="M133" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N133" s="3">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="O133" s="3">
-        <v>147</v>
-      </c>
-      <c r="P133" s="3">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="P133" s="3"/>
+    </row>
+    <row r="134" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C134" s="3">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="E134" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="F134" s="3"/>
       <c r="G134" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="K134" s="2"/>
-      <c r="L134" s="3"/>
-      <c r="M134" s="3"/>
+      <c r="I134" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L134" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="M134" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N134" s="3">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="O134" s="3">
-        <v>145</v>
-      </c>
-      <c r="P134" s="3"/>
-    </row>
-    <row r="135" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="P134" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C135" s="3">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3">
+        <v>127</v>
+      </c>
+      <c r="O135" s="3">
         <v>145</v>
       </c>
-      <c r="O135" s="3"/>
       <c r="P135" s="3"/>
     </row>
-    <row r="136" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C136" s="3">
-        <v>1947</v>
+        <v>2001</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3">
-        <v>5</v>
-      </c>
-      <c r="O136" s="3">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O136" s="3"/>
       <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C137" s="3">
-        <v>1969</v>
+        <v>1947</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E137" s="3"/>
-      <c r="F137" s="3" t="s">
-        <v>418</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F137" s="3"/>
       <c r="G137" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="I137" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="J137" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L137" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M137" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="K137" s="2"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
       <c r="N137" s="3">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="O137" s="3">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P137" s="3"/>
     </row>
-    <row r="138" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C138" s="3">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G138" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="I138" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="J138" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="K138" s="2"/>
-      <c r="L138" s="3"/>
-      <c r="M138" s="3"/>
+      <c r="K138" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N138" s="3">
         <v>148</v>
       </c>
       <c r="O138" s="3">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P138" s="3"/>
     </row>
-    <row r="139" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="3">
-        <v>1978</v>
+        <v>1957</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F139" s="3"/>
+      <c r="F139" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G139" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="J139" s="2" t="s">
         <v>427</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3">
-        <v>150</v>
-      </c>
-      <c r="O139" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="O139" s="3">
+        <v>151</v>
+      </c>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C140" s="3">
-        <v>2008</v>
+        <v>1978</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>364</v>
+        <v>69</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>428</v>
@@ -6689,179 +6703,184 @@
       <c r="G140" s="2" t="s">
         <v>429</v>
       </c>
+      <c r="J140" s="2" t="s">
+        <v>430</v>
+      </c>
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
+      <c r="N140" s="3">
+        <v>150</v>
+      </c>
       <c r="O140" s="3"/>
       <c r="P140" s="3"/>
     </row>
-    <row r="141" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C141" s="3">
-        <v>1969</v>
+        <v>2008</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
-      <c r="N141" s="3">
-        <v>149</v>
-      </c>
-      <c r="O141" s="3">
-        <v>150</v>
-      </c>
-      <c r="P141" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
+    </row>
+    <row r="142" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="C142" s="3">
-        <v>2003</v>
+        <v>1969</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3">
-        <v>145</v>
-      </c>
-      <c r="O142" s="3"/>
-      <c r="P142" s="3"/>
-    </row>
-    <row r="143" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="O142" s="3">
+        <v>150</v>
+      </c>
+      <c r="P142" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="C143" s="3">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>66</v>
+        <v>367</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="F143" s="3" t="s">
         <v>435</v>
       </c>
+      <c r="F143" s="3"/>
       <c r="G143" s="2" t="s">
         <v>436</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
-      <c r="N143" s="3"/>
+      <c r="N143" s="3">
+        <v>145</v>
+      </c>
       <c r="O143" s="3"/>
       <c r="P143" s="3"/>
     </row>
-    <row r="144" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C144" s="3">
-        <v>1945</v>
+        <v>2000</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>364</v>
+        <v>69</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F144" s="3"/>
+      <c r="F144" s="3" t="s">
+        <v>438</v>
+      </c>
       <c r="G144" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
-      <c r="N144" s="3">
-        <v>119</v>
-      </c>
+      <c r="N144" s="3"/>
       <c r="O144" s="3"/>
       <c r="P144" s="3"/>
     </row>
     <row r="145" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>336</v>
+        <v>16</v>
       </c>
       <c r="C145" s="3">
-        <v>2022</v>
+        <v>1945</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
-      <c r="N145" s="3"/>
+      <c r="N145" s="3">
+        <v>119</v>
+      </c>
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="C146" s="3">
-        <v>1973</v>
+        <v>2022</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="3"/>
@@ -6870,25 +6889,25 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c r="C147" s="3">
-        <v>2021</v>
+        <v>1973</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="3"/>
@@ -6899,99 +6918,126 @@
     </row>
     <row r="148" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C148" s="3">
-        <v>1972</v>
+        <v>2021</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3" t="s">
-        <v>445</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F148" s="3"/>
       <c r="G148" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="J148" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="K148" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="L148" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="M148" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N148" s="3">
-        <v>161</v>
-      </c>
+      <c r="K148" s="2"/>
+      <c r="L148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="C149" s="3">
-        <v>1986</v>
+        <v>1972</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F149" s="3"/>
       <c r="G149" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="K149" s="2"/>
-      <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
+      <c r="J149" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="M149" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N149" s="3">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C150" s="3">
-        <v>1945</v>
+        <v>1986</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E150" s="3"/>
-      <c r="F150" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F150" s="3"/>
       <c r="G150" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
+    </row>
+    <row r="151" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>162</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" s="3">
+        <v>1945</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K151" s="2"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3">
+        <v>2</v>
+      </c>
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D42100-E05C-4A01-B857-894301C1BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC29EA6-B6AE-45EC-9E99-74E8D8AB4DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="450">
   <si>
     <t>id</t>
   </si>
@@ -794,18 +794,6 @@
   </si>
   <si>
     <t>Touch / Pen Interaction / Mobile Computing</t>
-  </si>
-  <si>
-    <t>The Drift Table</t>
-  </si>
-  <si>
-    <t>שולחן סלון אלקטרוני המציג תצלומי אוויר הנעים באיטיות בהתאם לחלוקת המשקל על פניו. כאשר המשתמש מניח חפצים או נשען על אזור מסוים, התצוגה נעה בכיוון המתאים ומאפשרת לשוטט בנופים ללא יעד מוגדר. המכשיר תוכנן לעודד סקרנות, משחק והתבוננות בבית, ולא לביצוע משימה שימושית, ושימש למחקר על עיצוב טכנולוגיות המעודדות חקירה חופשית.</t>
-  </si>
-  <si>
-    <t>ויליאם גייבר הוא מעצב וחוקר אינטראקציה שהתעניין בחוויה האנושית מעבר ליעילות ולשימושיות. מחקריו עוסקים במשחק, סקרנות, עמימות ודרכים שבהן טכנולוגיה יכולה לקבל משמעות אישית בחיי היומיום.</t>
-  </si>
-  <si>
-    <t>Tangible Interaction / Ambient Interaction</t>
   </si>
   <si>
     <t>Reactable Live</t>
@@ -1583,8 +1571,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P151" totalsRowShown="0" dataDxfId="16">
-  <autoFilter ref="A1:P151" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P150" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:P150" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F164D471-F0AB-430B-A6FB-6338D8DB3E2B}" name="id" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{F5ED8843-E467-4E3B-864E-7412714707BF}" name="era" dataDxfId="14"/>
@@ -1892,7 +1880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:P150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1913,7 +1901,7 @@
     <col min="16" max="16" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4336,15 +4324,15 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="3">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>17</v>
@@ -4356,11 +4344,8 @@
       <c r="G70" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="H70" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="K70" s="2" t="s">
-        <v>248</v>
+        <v>144</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>145</v>
@@ -4374,7 +4359,7 @@
     </row>
     <row r="71" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>120</v>
@@ -4387,63 +4372,65 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="K71" s="2" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C72" s="3">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="K72" s="2" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N72" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N72" s="3">
+        <v>124</v>
+      </c>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
     <row r="73" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>120</v>
@@ -4456,62 +4443,67 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" s="3">
-        <v>124</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N73" s="3"/>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C74" s="3">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="K74" s="2" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
+      <c r="N74" s="3">
+        <v>142</v>
+      </c>
+      <c r="O74" s="3">
+        <v>120</v>
+      </c>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>120</v>
@@ -4524,102 +4516,91 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="K75" s="2" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="N75" s="3">
-        <v>142</v>
-      </c>
-      <c r="O75" s="3">
-        <v>120</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="3">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N76" s="3">
-        <v>141</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C77" s="3">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N77" s="3"/>
+        <v>262</v>
+      </c>
+      <c r="K77" s="2"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3">
+        <v>83</v>
+      </c>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>120</v>
@@ -4632,10 +4613,10 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="3"/>
@@ -4646,9 +4627,9 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>120</v>
@@ -4657,27 +4638,31 @@
         <v>2009</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K79" s="2"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3">
-        <v>83</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>120</v>
@@ -4690,13 +4675,16 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I80" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>115</v>
@@ -4704,16 +4692,22 @@
       <c r="M80" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N80" s="3"/>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-    </row>
-    <row r="81" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="N80" s="3">
+        <v>59</v>
+      </c>
+      <c r="O80" s="3">
+        <v>80</v>
+      </c>
+      <c r="P80" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="C81" s="3">
         <v>2009</v>
@@ -4723,16 +4717,16 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="I81" s="2" t="s">
         <v>273</v>
       </c>
+      <c r="H81" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="K81" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>115</v>
@@ -4740,25 +4734,19 @@
       <c r="M81" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N81" s="3">
-        <v>59</v>
-      </c>
-      <c r="O81" s="3">
-        <v>80</v>
-      </c>
-      <c r="P81" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C82" s="3">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>17</v>
@@ -4770,63 +4758,60 @@
       <c r="G82" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="H82" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="K82" s="2" t="s">
-        <v>279</v>
+        <v>22</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N82" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N82" s="3">
+        <v>125</v>
+      </c>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
     <row r="83" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C83" s="3">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="L83" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N83" s="3">
-        <v>125</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C84" s="3">
         <v>2011</v>
@@ -4836,30 +4821,30 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K84" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="L84" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C85" s="3">
         <v>2011</v>
@@ -4869,66 +4854,71 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="H85" s="2" t="s">
         <v>286</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>287</v>
+        <v>140</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C86" s="3">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="I86" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H86" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="K86" s="2" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N86" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N86" s="3">
+        <v>135</v>
+      </c>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
     <row r="87" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C87" s="3">
         <v>2013</v>
@@ -4938,35 +4928,33 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="I87" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="K87" s="2" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N87" s="3">
-        <v>135</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C88" s="3">
         <v>2013</v>
@@ -4976,33 +4964,30 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="L88" s="3" t="s">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C89" s="3">
         <v>2013</v>
@@ -5012,100 +4997,100 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="K89" s="2" t="s">
-        <v>299</v>
+        <v>145</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="N89" s="3">
+        <v>141</v>
+      </c>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
     <row r="90" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C90" s="3">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>145</v>
+        <v>283</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="N90" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C91" s="3">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" s="3">
-        <v>143</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C92" s="3">
         <v>2015</v>
@@ -5115,30 +5100,30 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C93" s="3">
         <v>2015</v>
@@ -5148,10 +5133,10 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>76</v>
@@ -5162,16 +5147,18 @@
       <c r="M93" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N93" s="3"/>
+      <c r="N93" s="3">
+        <v>105</v>
+      </c>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C94" s="3">
         <v>2015</v>
@@ -5181,35 +5168,36 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I94" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="K94" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="L94" s="3" t="s">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N94" s="3">
-        <v>105</v>
-      </c>
+      <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C95" s="3">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>17</v>
@@ -5221,28 +5209,25 @@
       <c r="G95" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I95" s="2" t="s">
+      <c r="K95" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="K95" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="L95" s="3" t="s">
-        <v>313</v>
+        <v>68</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C96" s="3">
         <v>2016</v>
@@ -5252,13 +5237,16 @@
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="J96" s="2" t="s">
         <v>315</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>316</v>
+        <v>68</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>68</v>
@@ -5270,12 +5258,12 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C97" s="3">
         <v>2016</v>
@@ -5285,19 +5273,16 @@
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="K97" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="J97" s="2" t="s">
+      <c r="L97" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M97" s="3" t="s">
         <v>62</v>
@@ -5306,15 +5291,15 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C98" s="3">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>17</v>
@@ -5330,10 +5315,10 @@
         <v>322</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>323</v>
+        <v>115</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
@@ -5341,32 +5326,32 @@
     </row>
     <row r="99" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C99" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="K99" s="2" t="s">
-        <v>326</v>
+        <v>145</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
@@ -5374,46 +5359,53 @@
     </row>
     <row r="100" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C100" s="3">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="K100" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K100" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="L100" s="3" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N100" s="3"/>
-      <c r="O100" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="N100" s="3">
+        <v>26</v>
+      </c>
+      <c r="O100" s="3">
+        <v>128</v>
+      </c>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C101" s="3">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>17</v>
@@ -5425,67 +5417,60 @@
       <c r="G101" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H101" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="K101" s="2" t="s">
-        <v>332</v>
+        <v>76</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="N101" s="3">
-        <v>26</v>
-      </c>
-      <c r="O101" s="3">
-        <v>128</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C102" s="3">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N102" s="3">
-        <v>96</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C103" s="3">
         <v>2021</v>
@@ -5495,19 +5480,19 @@
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
@@ -5515,43 +5500,48 @@
     </row>
     <row r="104" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
       <c r="C104" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="I104" s="2" t="s">
         <v>338</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N104" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="N104" s="3">
+        <v>138</v>
+      </c>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C105" s="3">
         <v>2022</v>
@@ -5561,16 +5551,19 @@
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="H105" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>342</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>126</v>
+        <v>343</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>126</v>
@@ -5584,53 +5577,45 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C106" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H106" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="K106" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="K106" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="L106" s="3" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N106" s="3">
-        <v>138</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N106" s="3"/>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C107" s="3">
         <v>2023</v>
@@ -5640,19 +5625,19 @@
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="K107" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K107" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="L107" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -5660,10 +5645,10 @@
     </row>
     <row r="108" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C108" s="3">
         <v>2023</v>
@@ -5673,30 +5658,32 @@
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="K108" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="L108" s="3" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N108" s="3"/>
+        <v>116</v>
+      </c>
+      <c r="N108" s="3">
+        <v>138</v>
+      </c>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C109" s="3">
         <v>2023</v>
@@ -5706,13 +5693,13 @@
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="K109" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>115</v>
@@ -5726,28 +5713,28 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C110" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="L110" s="3" t="s">
         <v>115</v>
@@ -5761,12 +5748,12 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C111" s="3">
         <v>2024</v>
@@ -5776,19 +5763,19 @@
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>356</v>
+        <v>126</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="N111" s="3">
         <v>138</v>
@@ -5796,319 +5783,317 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C112" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H112" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="K112" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="K112" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="L112" s="3" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N112" s="3">
-        <v>138</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N112" s="3"/>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="C113" s="3">
-        <v>2025</v>
+        <v>1945</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3" t="s">
         <v>363</v>
       </c>
+      <c r="E113" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F113" s="3"/>
       <c r="G113" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="H113" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="K113" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N113" s="3"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3">
+        <v>156</v>
+      </c>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C114" s="3">
-        <v>1945</v>
+        <v>2007</v>
       </c>
       <c r="D114" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F114" s="3"/>
-      <c r="G114" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C115" s="3">
-        <v>2007</v>
+        <v>1973</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C116" s="3">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3" t="s">
-        <v>372</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F116" s="3"/>
       <c r="G116" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3">
-        <v>21</v>
-      </c>
-      <c r="O116" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="O116" s="3">
+        <v>129</v>
+      </c>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C117" s="3">
-        <v>1969</v>
+        <v>2006</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="2" t="s">
-        <v>375</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G117" s="2"/>
       <c r="K117" s="2"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3">
-        <v>13</v>
-      </c>
-      <c r="O117" s="3">
-        <v>129</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="O117" s="3"/>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C118" s="3">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="G118" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="K118" s="2"/>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
     <row r="119" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C119" s="3">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E119" s="3"/>
+        <v>363</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>376</v>
+      </c>
       <c r="F119" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3">
+        <v>144</v>
+      </c>
+      <c r="O119" s="3">
+        <v>146</v>
+      </c>
+      <c r="P119" s="3"/>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A120" s="3">
+        <v>128</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C120" s="3">
+        <v>2011</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="O119" s="3"/>
-      <c r="P119" s="3"/>
-    </row>
-    <row r="120" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
-        <v>127</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C120" s="3">
-        <v>1986</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>380</v>
-      </c>
+      <c r="E120" s="3"/>
       <c r="F120" s="3" t="s">
-        <v>381</v>
+        <v>325</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3">
-        <v>144</v>
-      </c>
-      <c r="O120" s="3">
-        <v>146</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="C121" s="3">
-        <v>2011</v>
+        <v>1991</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3" t="s">
-        <v>329</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F121" s="3"/>
       <c r="G121" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3">
-        <v>104</v>
-      </c>
-      <c r="O121" s="3"/>
-      <c r="P121" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="O121" s="3">
+        <v>29</v>
+      </c>
+      <c r="P121" s="3">
+        <v>44</v>
+      </c>
     </row>
     <row r="122" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>137</v>
@@ -6117,47 +6102,41 @@
         <v>1991</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-      <c r="N122" s="3">
-        <v>2</v>
-      </c>
-      <c r="O122" s="3">
-        <v>29</v>
-      </c>
-      <c r="P122" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N122" s="3"/>
+      <c r="O122" s="3"/>
+      <c r="P122" s="3"/>
+    </row>
+    <row r="123" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>137</v>
+        <v>271</v>
       </c>
       <c r="C123" s="3">
-        <v>1991</v>
+        <v>2010</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="3"/>
@@ -6166,25 +6145,25 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C124" s="3">
-        <v>2010</v>
+        <v>1965</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="3"/>
@@ -6193,694 +6172,694 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="C125" s="3">
-        <v>1965</v>
+        <v>2020</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
-      <c r="O125" s="3"/>
-      <c r="P125" s="3"/>
-    </row>
-    <row r="126" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N125" s="3">
+        <v>89</v>
+      </c>
+      <c r="O125" s="3">
+        <v>105</v>
+      </c>
+      <c r="P125" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C126" s="3">
-        <v>2020</v>
+        <v>1929</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
-      <c r="N126" s="3">
-        <v>89</v>
-      </c>
-      <c r="O126" s="3">
-        <v>105</v>
-      </c>
-      <c r="P126" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="P126" s="3"/>
+    </row>
+    <row r="127" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c r="C127" s="3">
-        <v>1929</v>
+        <v>2022</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>367</v>
+        <v>69</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
-      <c r="O127" s="3"/>
+      <c r="N127" s="3">
+        <v>108</v>
+      </c>
+      <c r="O127" s="3">
+        <v>109</v>
+      </c>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="C128" s="3">
-        <v>2022</v>
+        <v>1983</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3">
-        <v>108</v>
-      </c>
-      <c r="O128" s="3">
-        <v>109</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O128" s="3"/>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C129" s="3">
-        <v>1983</v>
+        <v>1997</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>398</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3">
-        <v>23</v>
-      </c>
-      <c r="O129" s="3"/>
-      <c r="P129" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="O129" s="3">
+        <v>50</v>
+      </c>
+      <c r="P129" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="130" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C130" s="3">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3">
-        <v>55</v>
-      </c>
-      <c r="O130" s="3">
-        <v>50</v>
-      </c>
-      <c r="P130" s="3">
-        <v>58</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="O130" s="3"/>
+      <c r="P130" s="3"/>
     </row>
     <row r="131" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>120</v>
+        <v>271</v>
       </c>
       <c r="C131" s="3">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="O131" s="3"/>
       <c r="P131" s="3"/>
     </row>
-    <row r="132" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="C132" s="3">
-        <v>2014</v>
+        <v>1986</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I132" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="F132" s="3"/>
-      <c r="G132" s="2" t="s">
+      <c r="K132" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="K132" s="2"/>
-      <c r="L132" s="3"/>
-      <c r="M132" s="3"/>
+      <c r="L132" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M132" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N132" s="3">
-        <v>93</v>
-      </c>
-      <c r="O132" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="O132" s="3">
+        <v>20</v>
+      </c>
       <c r="P132" s="3"/>
     </row>
-    <row r="133" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C133" s="3">
-        <v>1986</v>
+        <v>2001</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L133" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="M133" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N133" s="3">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="O133" s="3">
-        <v>20</v>
-      </c>
-      <c r="P133" s="3"/>
-    </row>
-    <row r="134" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="P133" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C134" s="3">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E134" s="3"/>
-      <c r="F134" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="F134" s="3"/>
+      <c r="G134" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L134" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="M134" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="K134" s="2"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
       <c r="N134" s="3">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="O134" s="3">
+        <v>145</v>
+      </c>
+      <c r="P134" s="3"/>
+    </row>
+    <row r="135" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
         <v>147</v>
-      </c>
-      <c r="P134" s="3">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C135" s="3">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3">
-        <v>127</v>
-      </c>
-      <c r="O135" s="3">
         <v>145</v>
       </c>
+      <c r="O135" s="3"/>
       <c r="P135" s="3"/>
     </row>
-    <row r="136" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C136" s="3">
-        <v>2001</v>
+        <v>1947</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3">
-        <v>145</v>
-      </c>
-      <c r="O136" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="O136" s="3">
+        <v>150</v>
+      </c>
       <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C137" s="3">
-        <v>1947</v>
+        <v>1969</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E137" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I137" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="F137" s="3"/>
-      <c r="G137" s="2" t="s">
+      <c r="J137" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="K137" s="2"/>
-      <c r="L137" s="3"/>
-      <c r="M137" s="3"/>
+      <c r="K137" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N137" s="3">
-        <v>5</v>
+        <v>148</v>
       </c>
       <c r="O137" s="3">
+        <v>153</v>
+      </c>
+      <c r="P137" s="3"/>
+    </row>
+    <row r="138" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
         <v>150</v>
-      </c>
-      <c r="P137" s="3"/>
-    </row>
-    <row r="138" spans="1:16" ht="114" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C138" s="3">
-        <v>1969</v>
+        <v>1957</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E138" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>421</v>
+      </c>
       <c r="F138" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="I138" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="J138" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="K138" s="2"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3"/>
       <c r="N138" s="3">
         <v>148</v>
       </c>
       <c r="O138" s="3">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P138" s="3"/>
     </row>
-    <row r="139" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="3">
-        <v>1957</v>
+        <v>1978</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E139" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F139" s="3"/>
+      <c r="G139" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="J139" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3">
-        <v>148</v>
-      </c>
-      <c r="O139" s="3">
-        <v>151</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C140" s="3">
-        <v>1978</v>
+        <v>2008</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
-      <c r="N140" s="3">
-        <v>150</v>
-      </c>
+      <c r="N140" s="3"/>
       <c r="O140" s="3"/>
       <c r="P140" s="3"/>
     </row>
-    <row r="141" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C141" s="3">
-        <v>2008</v>
+        <v>1969</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-      <c r="O141" s="3"/>
-      <c r="P141" s="3"/>
-    </row>
-    <row r="142" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="N141" s="3">
+        <v>149</v>
+      </c>
+      <c r="O141" s="3">
+        <v>150</v>
+      </c>
+      <c r="P141" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C142" s="3">
-        <v>1969</v>
+        <v>2003</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3">
-        <v>149</v>
-      </c>
-      <c r="O142" s="3">
-        <v>150</v>
-      </c>
-      <c r="P142" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+        <v>145</v>
+      </c>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+    </row>
+    <row r="143" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C143" s="3">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>367</v>
+        <v>69</v>
       </c>
       <c r="E143" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="F143" s="3"/>
-      <c r="G143" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
-      <c r="N143" s="3">
-        <v>145</v>
-      </c>
+      <c r="N143" s="3"/>
       <c r="O143" s="3"/>
       <c r="P143" s="3"/>
     </row>
-    <row r="144" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="C144" s="3">
-        <v>2000</v>
+        <v>1945</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="E144" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F144" s="3"/>
+      <c r="G144" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
-      <c r="N144" s="3"/>
+      <c r="N144" s="3">
+        <v>119</v>
+      </c>
       <c r="O144" s="3"/>
       <c r="P144" s="3"/>
     </row>
     <row r="145" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c r="C145" s="3">
-        <v>1945</v>
+        <v>2022</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
-      <c r="N145" s="3">
-        <v>119</v>
-      </c>
+      <c r="N145" s="3"/>
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="C146" s="3">
-        <v>2022</v>
+        <v>1973</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="3"/>
@@ -6889,25 +6868,25 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="C147" s="3">
-        <v>1973</v>
+        <v>2021</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="3"/>
@@ -6918,126 +6897,99 @@
     </row>
     <row r="148" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>275</v>
+        <v>16</v>
       </c>
       <c r="C148" s="3">
-        <v>2021</v>
+        <v>1972</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="3"/>
+      <c r="F148" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="J148" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F148" s="3"/>
-      <c r="G148" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="K148" s="2"/>
-      <c r="L148" s="3"/>
-      <c r="M148" s="3"/>
-      <c r="N148" s="3"/>
+      <c r="K148" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M148" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N148" s="3">
+        <v>161</v>
+      </c>
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
+        <v>161</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C149" s="3">
+        <v>1986</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F149" s="3"/>
+      <c r="G149" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K149" s="2"/>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3">
         <v>160</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" s="3">
-        <v>1972</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E149" s="3"/>
-      <c r="F149" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="L149" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="M149" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N149" s="3">
-        <v>161</v>
       </c>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C150" s="3">
-        <v>1986</v>
+        <v>1945</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E150" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="F150" s="3"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G150" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
-    </row>
-    <row r="151" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
-        <v>162</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" s="3">
-        <v>1945</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="K151" s="2"/>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3">
-        <v>2</v>
-      </c>
-      <c r="O151" s="3"/>
-      <c r="P151" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romis\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC29EA6-B6AE-45EC-9E99-74E8D8AB4DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D42100-E05C-4A01-B857-894301C1BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="454">
   <si>
     <t>id</t>
   </si>
@@ -794,6 +794,18 @@
   </si>
   <si>
     <t>Touch / Pen Interaction / Mobile Computing</t>
+  </si>
+  <si>
+    <t>The Drift Table</t>
+  </si>
+  <si>
+    <t>שולחן סלון אלקטרוני המציג תצלומי אוויר הנעים באיטיות בהתאם לחלוקת המשקל על פניו. כאשר המשתמש מניח חפצים או נשען על אזור מסוים, התצוגה נעה בכיוון המתאים ומאפשרת לשוטט בנופים ללא יעד מוגדר. המכשיר תוכנן לעודד סקרנות, משחק והתבוננות בבית, ולא לביצוע משימה שימושית, ושימש למחקר על עיצוב טכנולוגיות המעודדות חקירה חופשית.</t>
+  </si>
+  <si>
+    <t>ויליאם גייבר הוא מעצב וחוקר אינטראקציה שהתעניין בחוויה האנושית מעבר ליעילות ולשימושיות. מחקריו עוסקים במשחק, סקרנות, עמימות ודרכים שבהן טכנולוגיה יכולה לקבל משמעות אישית בחיי היומיום.</t>
+  </si>
+  <si>
+    <t>Tangible Interaction / Ambient Interaction</t>
   </si>
   <si>
     <t>Reactable Live</t>
@@ -1571,8 +1583,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P150" totalsRowShown="0" dataDxfId="16">
-  <autoFilter ref="A1:P150" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}" name="טבלה1" displayName="טבלה1" ref="A1:P151" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:P151" xr:uid="{1A74C817-109F-4704-9B2F-538DE84653E7}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{F164D471-F0AB-430B-A6FB-6338D8DB3E2B}" name="id" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{F5ED8843-E467-4E3B-864E-7412714707BF}" name="era" dataDxfId="14"/>
@@ -1880,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1901,7 +1913,7 @@
     <col min="16" max="16" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4324,15 +4336,15 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>17</v>
@@ -4344,8 +4356,11 @@
       <c r="G70" s="2" t="s">
         <v>246</v>
       </c>
+      <c r="H70" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="K70" s="2" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>145</v>
@@ -4359,7 +4374,7 @@
     </row>
     <row r="71" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>120</v>
@@ -4372,65 +4387,63 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
     </row>
-    <row r="72" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C72" s="3">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N72" s="3">
-        <v>124</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
     <row r="73" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>120</v>
@@ -4443,67 +4456,62 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N73" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N73" s="3">
+        <v>124</v>
+      </c>
       <c r="O73" s="3"/>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C74" s="3">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>244</v>
+        <v>181</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="N74" s="3">
-        <v>142</v>
-      </c>
-      <c r="O74" s="3">
-        <v>120</v>
-      </c>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>120</v>
@@ -4516,91 +4524,102 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>145</v>
+        <v>244</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>146</v>
+        <v>58</v>
       </c>
       <c r="N75" s="3">
-        <v>141</v>
-      </c>
-      <c r="O75" s="3"/>
+        <v>142</v>
+      </c>
+      <c r="O75" s="3">
+        <v>120</v>
+      </c>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C76" s="3">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N76" s="3"/>
+        <v>146</v>
+      </c>
+      <c r="N76" s="3">
+        <v>141</v>
+      </c>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
     </row>
-    <row r="77" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C77" s="3">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3">
-        <v>83</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N77" s="3"/>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>120</v>
@@ -4613,10 +4632,10 @@
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="3"/>
@@ -4627,9 +4646,9 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
     </row>
-    <row r="79" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>120</v>
@@ -4638,31 +4657,27 @@
         <v>2009</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N79" s="3"/>
+        <v>268</v>
+      </c>
+      <c r="K79" s="2"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3">
+        <v>83</v>
+      </c>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>120</v>
@@ -4675,16 +4690,13 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>270</v>
+        <v>114</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>115</v>
@@ -4692,22 +4704,16 @@
       <c r="M80" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N80" s="3">
-        <v>59</v>
-      </c>
-      <c r="O80" s="3">
-        <v>80</v>
-      </c>
-      <c r="P80" s="3">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="C81" s="3">
         <v>2009</v>
@@ -4717,16 +4723,16 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="I81" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="H81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>115</v>
@@ -4734,19 +4740,25 @@
       <c r="M81" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="N81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="N81" s="3">
+        <v>59</v>
+      </c>
+      <c r="O81" s="3">
+        <v>80</v>
+      </c>
+      <c r="P81" s="3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C82" s="3">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>17</v>
@@ -4758,60 +4770,63 @@
       <c r="G82" s="2" t="s">
         <v>277</v>
       </c>
+      <c r="H82" s="2" t="s">
+        <v>278</v>
+      </c>
       <c r="K82" s="2" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N82" s="3">
-        <v>125</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
     <row r="83" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C83" s="3">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>280</v>
+        <v>22</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="N83" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N83" s="3">
+        <v>125</v>
+      </c>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
     </row>
-    <row r="84" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C84" s="3">
         <v>2011</v>
@@ -4821,30 +4836,30 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C85" s="3">
         <v>2011</v>
@@ -4854,71 +4869,66 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H85" s="2" t="s">
         <v>286</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
     </row>
-    <row r="86" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C86" s="3">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I86" s="2" t="s">
         <v>289</v>
       </c>
+      <c r="H86" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="K86" s="2" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N86" s="3">
-        <v>135</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
     </row>
     <row r="87" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C87" s="3">
         <v>2013</v>
@@ -4928,33 +4938,35 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>275</v>
+        <v>173</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N87" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N87" s="3">
+        <v>135</v>
+      </c>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
     </row>
-    <row r="88" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C88" s="3">
         <v>2013</v>
@@ -4964,30 +4976,33 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>296</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
     </row>
-    <row r="89" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C89" s="3">
         <v>2013</v>
@@ -4997,100 +5012,100 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="N89" s="3">
-        <v>141</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="N89" s="3"/>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
     <row r="90" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C90" s="3">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>283</v>
+        <v>145</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>46</v>
+        <v>145</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="N90" s="3">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
     </row>
-    <row r="91" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C91" s="3">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N91" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="N91" s="3">
+        <v>143</v>
+      </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C92" s="3">
         <v>2015</v>
@@ -5100,30 +5115,30 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
     </row>
-    <row r="93" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C93" s="3">
         <v>2015</v>
@@ -5133,10 +5148,10 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>76</v>
@@ -5147,18 +5162,16 @@
       <c r="M93" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N93" s="3">
-        <v>105</v>
-      </c>
+      <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
     </row>
-    <row r="94" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C94" s="3">
         <v>2015</v>
@@ -5168,36 +5181,35 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>309</v>
+        <v>76</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>309</v>
+        <v>76</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N94" s="3"/>
+      <c r="N94" s="3">
+        <v>105</v>
+      </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C95" s="3">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>17</v>
@@ -5209,25 +5221,28 @@
       <c r="G95" s="2" t="s">
         <v>311</v>
       </c>
+      <c r="I95" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="K95" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>68</v>
+        <v>313</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C96" s="3">
         <v>2016</v>
@@ -5237,16 +5252,13 @@
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J96" s="2" t="s">
         <v>315</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>68</v>
+        <v>316</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>68</v>
@@ -5258,12 +5270,12 @@
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C97" s="3">
         <v>2016</v>
@@ -5273,16 +5285,19 @@
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>318</v>
+        <v>68</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>319</v>
+        <v>68</v>
       </c>
       <c r="M97" s="3" t="s">
         <v>62</v>
@@ -5291,15 +5306,15 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C98" s="3">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>17</v>
@@ -5315,10 +5330,10 @@
         <v>322</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>115</v>
+        <v>323</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
@@ -5326,32 +5341,32 @@
     </row>
     <row r="99" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C99" s="3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>145</v>
+        <v>326</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
@@ -5359,53 +5374,46 @@
     </row>
     <row r="100" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C100" s="3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>328</v>
+        <v>145</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N100" s="3">
-        <v>26</v>
-      </c>
-      <c r="O100" s="3">
-        <v>128</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
       <c r="P100" s="3"/>
     </row>
-    <row r="101" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C101" s="3">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>17</v>
@@ -5417,60 +5425,67 @@
       <c r="G101" s="2" t="s">
         <v>330</v>
       </c>
+      <c r="H101" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="K101" s="2" t="s">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="N101" s="3">
-        <v>96</v>
-      </c>
-      <c r="O101" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="O101" s="3">
+        <v>128</v>
+      </c>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C102" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N102" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="N102" s="3">
+        <v>96</v>
+      </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
     </row>
-    <row r="103" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C103" s="3">
         <v>2021</v>
@@ -5480,19 +5495,19 @@
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
@@ -5500,48 +5515,43 @@
     </row>
     <row r="104" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>335</v>
+        <v>275</v>
       </c>
       <c r="C104" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="I104" s="2" t="s">
         <v>338</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="N104" s="3">
-        <v>138</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="N104" s="3"/>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
     </row>
-    <row r="105" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C105" s="3">
         <v>2022</v>
@@ -5551,19 +5561,16 @@
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="H105" s="2" t="s">
         <v>341</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>342</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>343</v>
+        <v>126</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>126</v>
@@ -5577,45 +5584,53 @@
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
     </row>
-    <row r="106" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C106" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="H106" s="2" t="s">
         <v>345</v>
       </c>
+      <c r="I106" s="2" t="s">
+        <v>346</v>
+      </c>
       <c r="K106" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N106" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="N106" s="3">
+        <v>138</v>
+      </c>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C107" s="3">
         <v>2023</v>
@@ -5625,19 +5640,19 @@
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -5645,10 +5660,10 @@
     </row>
     <row r="108" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C108" s="3">
         <v>2023</v>
@@ -5658,32 +5673,30 @@
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N108" s="3">
-        <v>138</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N108" s="3"/>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
     </row>
-    <row r="109" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C109" s="3">
         <v>2023</v>
@@ -5693,13 +5706,13 @@
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>115</v>
@@ -5713,28 +5726,28 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C110" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G110" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="K110" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="L110" s="3" t="s">
         <v>115</v>
@@ -5748,12 +5761,12 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C111" s="3">
         <v>2024</v>
@@ -5763,19 +5776,19 @@
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>126</v>
+        <v>356</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="N111" s="3">
         <v>138</v>
@@ -5783,317 +5796,319 @@
       <c r="O111" s="3"/>
       <c r="P111" s="3"/>
     </row>
-    <row r="112" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C112" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N112" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="N112" s="3">
+        <v>138</v>
+      </c>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
     </row>
-    <row r="113" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="C113" s="3">
-        <v>1945</v>
+        <v>2025</v>
       </c>
       <c r="D113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="G113" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F113" s="3"/>
-      <c r="G113" s="2" t="s">
+      <c r="H113" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="K113" s="2"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3">
-        <v>156</v>
-      </c>
+      <c r="K113" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N113" s="3"/>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
     </row>
-    <row r="114" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C114" s="3">
-        <v>2007</v>
+        <v>1945</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3" t="s">
-        <v>366</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F114" s="3"/>
       <c r="G114" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
       <c r="M114" s="3"/>
       <c r="N114" s="3">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C115" s="3">
-        <v>1973</v>
+        <v>2007</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3"/>
       <c r="N115" s="3">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
     </row>
-    <row r="116" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C116" s="3">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F116" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="G116" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
       <c r="M116" s="3"/>
       <c r="N116" s="3">
-        <v>13</v>
-      </c>
-      <c r="O116" s="3">
-        <v>129</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="O116" s="3"/>
       <c r="P116" s="3"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C117" s="3">
-        <v>2006</v>
+        <v>1969</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="G117" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="K117" s="2"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3">
-        <v>75</v>
-      </c>
-      <c r="O117" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="O117" s="3">
+        <v>129</v>
+      </c>
       <c r="P117" s="3"/>
     </row>
-    <row r="118" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C118" s="3">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>375</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="G118" s="2"/>
       <c r="K118" s="2"/>
       <c r="L118" s="3"/>
       <c r="M118" s="3"/>
       <c r="N118" s="3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
     </row>
     <row r="119" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C119" s="3">
-        <v>1986</v>
+        <v>2003</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>376</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E119" s="3"/>
       <c r="F119" s="3" t="s">
         <v>377</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>378</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3"/>
       <c r="N119" s="3">
-        <v>144</v>
-      </c>
-      <c r="O119" s="3">
-        <v>146</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="O119" s="3"/>
       <c r="P119" s="3"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>271</v>
+        <v>84</v>
       </c>
       <c r="C120" s="3">
-        <v>2011</v>
+        <v>1986</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E120" s="3"/>
+        <v>367</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="F120" s="3" t="s">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
       <c r="M120" s="3"/>
       <c r="N120" s="3">
-        <v>104</v>
-      </c>
-      <c r="O120" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="O120" s="3">
+        <v>146</v>
+      </c>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>137</v>
+        <v>275</v>
       </c>
       <c r="C121" s="3">
-        <v>1991</v>
+        <v>2011</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F121" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G121" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3">
-        <v>2</v>
-      </c>
-      <c r="O121" s="3">
-        <v>29</v>
-      </c>
-      <c r="P121" s="3">
-        <v>44</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="O121" s="3"/>
+      <c r="P121" s="3"/>
     </row>
     <row r="122" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>137</v>
@@ -6102,41 +6117,47 @@
         <v>1991</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>363</v>
+        <v>69</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
       <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
-      <c r="O122" s="3"/>
-      <c r="P122" s="3"/>
-    </row>
-    <row r="123" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+      <c r="N122" s="3">
+        <v>2</v>
+      </c>
+      <c r="O122" s="3">
+        <v>29</v>
+      </c>
+      <c r="P122" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="C123" s="3">
-        <v>2010</v>
+        <v>1991</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="3"/>
@@ -6145,25 +6166,25 @@
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
     </row>
-    <row r="124" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C124" s="3">
-        <v>1965</v>
+        <v>2010</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="3"/>
@@ -6172,694 +6193,694 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c r="C125" s="3">
-        <v>2020</v>
+        <v>1965</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
       <c r="M125" s="3"/>
-      <c r="N125" s="3">
-        <v>89</v>
-      </c>
-      <c r="O125" s="3">
-        <v>105</v>
-      </c>
-      <c r="P125" s="3">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+    </row>
+    <row r="126" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C126" s="3">
-        <v>1929</v>
+        <v>2020</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-      <c r="O126" s="3"/>
-      <c r="P126" s="3"/>
-    </row>
-    <row r="127" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="N126" s="3">
+        <v>89</v>
+      </c>
+      <c r="O126" s="3">
+        <v>105</v>
+      </c>
+      <c r="P126" s="3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="C127" s="3">
-        <v>2022</v>
+        <v>1929</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>69</v>
+        <v>367</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
-      <c r="N127" s="3">
-        <v>108</v>
-      </c>
-      <c r="O127" s="3">
-        <v>109</v>
-      </c>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
       <c r="P127" s="3"/>
     </row>
-    <row r="128" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="C128" s="3">
-        <v>1983</v>
+        <v>2022</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3">
-        <v>23</v>
-      </c>
-      <c r="O128" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="O128" s="3">
+        <v>109</v>
+      </c>
       <c r="P128" s="3"/>
     </row>
-    <row r="129" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C129" s="3">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="3"/>
       <c r="M129" s="3"/>
       <c r="N129" s="3">
-        <v>55</v>
-      </c>
-      <c r="O129" s="3">
-        <v>50</v>
-      </c>
-      <c r="P129" s="3">
-        <v>58</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="O129" s="3"/>
+      <c r="P129" s="3"/>
     </row>
     <row r="130" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C130" s="3">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>402</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3"/>
       <c r="N130" s="3">
-        <v>77</v>
-      </c>
-      <c r="O130" s="3"/>
-      <c r="P130" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="O130" s="3">
+        <v>50</v>
+      </c>
+      <c r="P130" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="131" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>271</v>
+        <v>120</v>
       </c>
       <c r="C131" s="3">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="3"/>
       <c r="M131" s="3"/>
       <c r="N131" s="3">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="O131" s="3"/>
       <c r="P131" s="3"/>
     </row>
-    <row r="132" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:16" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
+        <v>143</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="3">
+        <v>2014</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F132" s="3"/>
+      <c r="G132" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K132" s="2"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3">
+        <v>93</v>
+      </c>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3"/>
+    </row>
+    <row r="133" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
         <v>144</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B133" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C133" s="3">
         <v>1986</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L132" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M132" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N132" s="3">
-        <v>127</v>
-      </c>
-      <c r="O132" s="3">
-        <v>20</v>
-      </c>
-      <c r="P132" s="3"/>
-    </row>
-    <row r="133" spans="1:16" ht="171" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>145</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C133" s="3">
-        <v>2001</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="I133" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="K133" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="L133" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="M133" s="3" t="s">
         <v>77</v>
       </c>
       <c r="N133" s="3">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="O133" s="3">
-        <v>147</v>
-      </c>
-      <c r="P133" s="3">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="P133" s="3"/>
+    </row>
+    <row r="134" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C134" s="3">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E134" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="3"/>
+      <c r="F134" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L134" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="F134" s="3"/>
-      <c r="G134" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="K134" s="2"/>
-      <c r="L134" s="3"/>
-      <c r="M134" s="3"/>
+      <c r="M134" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="N134" s="3">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="O134" s="3">
-        <v>145</v>
-      </c>
-      <c r="P134" s="3"/>
-    </row>
-    <row r="135" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="P134" s="3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C135" s="3">
-        <v>2001</v>
+        <v>2011</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3"/>
       <c r="N135" s="3">
+        <v>127</v>
+      </c>
+      <c r="O135" s="3">
         <v>145</v>
       </c>
-      <c r="O135" s="3"/>
       <c r="P135" s="3"/>
     </row>
-    <row r="136" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C136" s="3">
-        <v>1947</v>
+        <v>2001</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3">
-        <v>5</v>
-      </c>
-      <c r="O136" s="3">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O136" s="3"/>
       <c r="P136" s="3"/>
     </row>
     <row r="137" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C137" s="3">
-        <v>1969</v>
+        <v>1947</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E137" s="3"/>
-      <c r="F137" s="3" t="s">
-        <v>417</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F137" s="3"/>
       <c r="G137" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J137" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="K137" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L137" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M137" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="K137" s="2"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
       <c r="N137" s="3">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="O137" s="3">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P137" s="3"/>
     </row>
-    <row r="138" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C138" s="3">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="3"/>
+      <c r="F138" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="G138" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="I138" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="K138" s="2"/>
-      <c r="L138" s="3"/>
-      <c r="M138" s="3"/>
+      <c r="J138" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="N138" s="3">
         <v>148</v>
       </c>
       <c r="O138" s="3">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P138" s="3"/>
     </row>
-    <row r="139" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:16" ht="185.25" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="3">
-        <v>1978</v>
+        <v>1957</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F139" s="3"/>
+        <v>425</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>426</v>
+      </c>
       <c r="G139" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J139" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3">
-        <v>150</v>
-      </c>
-      <c r="O139" s="3"/>
+        <v>148</v>
+      </c>
+      <c r="O139" s="3">
+        <v>151</v>
+      </c>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C140" s="3">
-        <v>2008</v>
+        <v>1978</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>363</v>
+        <v>69</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>430</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
       <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
+      <c r="N140" s="3">
+        <v>150</v>
+      </c>
       <c r="O140" s="3"/>
       <c r="P140" s="3"/>
     </row>
-    <row r="141" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="C141" s="3">
-        <v>1969</v>
+        <v>2008</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
       <c r="M141" s="3"/>
-      <c r="N141" s="3">
-        <v>149</v>
-      </c>
-      <c r="O141" s="3">
-        <v>150</v>
-      </c>
-      <c r="P141" s="3">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
+    </row>
+    <row r="142" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="C142" s="3">
-        <v>2003</v>
+        <v>1969</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3">
-        <v>145</v>
-      </c>
-      <c r="O142" s="3"/>
-      <c r="P142" s="3"/>
-    </row>
-    <row r="143" spans="1:16" ht="171" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="O142" s="3">
+        <v>150</v>
+      </c>
+      <c r="P142" s="3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C143" s="3">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>69</v>
+        <v>367</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>434</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="F143" s="3"/>
       <c r="G143" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
       <c r="M143" s="3"/>
-      <c r="N143" s="3"/>
+      <c r="N143" s="3">
+        <v>145</v>
+      </c>
       <c r="O143" s="3"/>
       <c r="P143" s="3"/>
     </row>
-    <row r="144" spans="1:16" ht="114" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:16" ht="171" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C144" s="3">
-        <v>1945</v>
+        <v>2000</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>363</v>
+        <v>69</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F144" s="3"/>
+        <v>437</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>438</v>
+      </c>
       <c r="G144" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
-      <c r="N144" s="3">
-        <v>119</v>
-      </c>
+      <c r="N144" s="3"/>
       <c r="O144" s="3"/>
       <c r="P144" s="3"/>
     </row>
     <row r="145" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c r="C145" s="3">
-        <v>2022</v>
+        <v>1945</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3"/>
-      <c r="N145" s="3"/>
+      <c r="N145" s="3">
+        <v>119</v>
+      </c>
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:16" ht="114" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="C146" s="3">
-        <v>1973</v>
+        <v>2022</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="3"/>
@@ -6868,25 +6889,25 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c r="C147" s="3">
-        <v>2021</v>
+        <v>1973</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="3"/>
@@ -6897,99 +6918,126 @@
     </row>
     <row r="148" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>16</v>
+        <v>275</v>
       </c>
       <c r="C148" s="3">
-        <v>1972</v>
+        <v>2021</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E148" s="3"/>
-      <c r="F148" s="3" t="s">
-        <v>444</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="F148" s="3"/>
       <c r="G148" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="L148" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M148" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N148" s="3">
-        <v>161</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="K148" s="2"/>
+      <c r="L148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:16" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
+        <v>160</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="3">
+        <v>1972</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="3"/>
+      <c r="F149" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="M149" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N149" s="3">
         <v>161</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C149" s="3">
-        <v>1986</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="F149" s="3"/>
-      <c r="G149" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="K149" s="2"/>
-      <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="3">
-        <v>160</v>
       </c>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C150" s="3">
-        <v>1945</v>
+        <v>1986</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E150" s="3"/>
-      <c r="F150" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="E150" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F150" s="3"/>
       <c r="G150" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3"/>
       <c r="N150" s="3">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
+    </row>
+    <row r="151" spans="1:16" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>162</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" s="3">
+        <v>1945</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E151" s="3"/>
+      <c r="F151" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K151" s="2"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3">
+        <v>2</v>
+      </c>
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\romis\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D42100-E05C-4A01-B857-894301C1BFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A6CDCA-98CF-4B46-8C46-B864A28769C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <t>Theremin</t>
   </si>
   <si>
-    <t xml:space="preserve">כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
-</t>
-  </si>
-  <si>
     <t>לב טרמין היה פיזיקאי וממציא רוסי, שפעל בצומת שבין אלקטרוניקה, מוזיקה וטכנולוגיית חישה. חייו יוצאי הדופן כללו גם עבודה עבור שירותי המודיעין הסובייטיים ופיתוח טכנולוגיות האזנה.</t>
   </si>
   <si>
@@ -1467,6 +1463,10 @@
   </si>
   <si>
     <t>האיור של שולחן ה-Memex שפורסם במגזין Life בשנת 1945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST!!!!!!!!! כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
+</t>
   </si>
 </sst>
 </file>
@@ -1913,7 +1913,7 @@
     <col min="16" max="16" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1981,19 +1981,19 @@
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -2014,25 +2014,25 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="N3" s="3">
         <v>119</v>
@@ -2057,22 +2057,22 @@
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="N4" s="3">
         <v>35</v>
@@ -2095,19 +2095,19 @@
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -2128,19 +2128,19 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N6" s="3">
         <v>39</v>
@@ -2165,22 +2165,22 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N7" s="3">
         <v>122</v>
@@ -2203,22 +2203,22 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N8" s="3">
         <v>13</v>
@@ -2245,22 +2245,22 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -2281,19 +2281,19 @@
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -2314,19 +2314,19 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -2347,19 +2347,19 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="K12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="N12" s="3">
         <v>13</v>
@@ -2384,19 +2384,19 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="L13" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="M13" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -2413,16 +2413,16 @@
         <v>1968</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="3"/>
@@ -2452,22 +2452,22 @@
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -2488,22 +2488,22 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N16" s="3">
         <v>49</v>
@@ -2516,20 +2516,20 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="3">
         <v>1989</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="3"/>
@@ -2555,22 +2555,22 @@
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="K18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="K19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2627,19 +2627,19 @@
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="K20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2656,14 +2656,14 @@
         <v>1969</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="3"/>
@@ -2679,7 +2679,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="3">
         <v>1981</v>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="L22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N22" s="3">
         <v>121</v>
@@ -2714,7 +2714,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="3">
         <v>1983</v>
@@ -2724,19 +2724,19 @@
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="K23" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N23" s="3">
         <v>21</v>
@@ -2751,7 +2751,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="3">
         <v>1983</v>
@@ -2761,22 +2761,22 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="N24" s="3">
         <v>139</v>
@@ -2789,7 +2789,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3">
         <v>1984</v>
@@ -2799,22 +2799,22 @@
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="K25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N25" s="3">
         <v>21</v>
@@ -2831,7 +2831,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="3">
         <v>1984</v>
@@ -2841,22 +2841,22 @@
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -2867,7 +2867,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" s="3">
         <v>1984</v>
@@ -2877,22 +2877,22 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="K27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2903,20 +2903,20 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28" s="3">
         <v>2001</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="3"/>
@@ -2932,7 +2932,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3">
         <v>1987</v>
@@ -2942,19 +2942,19 @@
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2965,7 +2965,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3">
         <v>1987</v>
@@ -2975,25 +2975,25 @@
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="K30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="3" t="s">
+      <c r="M30" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="N30" s="3">
         <v>129</v>
@@ -3006,20 +3006,20 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C31" s="3">
         <v>2001</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="3"/>
@@ -3035,7 +3035,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="3">
         <v>1989</v>
@@ -3045,22 +3045,22 @@
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="K32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="M32" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N32" s="3">
         <v>16</v>
@@ -3075,7 +3075,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C33" s="3">
         <v>1990</v>
@@ -3085,19 +3085,19 @@
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M33" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -3108,7 +3108,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C34" s="3">
         <v>1990</v>
@@ -3118,19 +3118,19 @@
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="M34" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -3141,7 +3141,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C35" s="3">
         <v>1991</v>
@@ -3151,19 +3151,19 @@
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="L35" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -3180,14 +3180,14 @@
         <v>1949</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="3"/>
@@ -3203,7 +3203,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" s="3">
         <v>1992</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="K37" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M37" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -3239,7 +3239,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38" s="3">
         <v>1992</v>
@@ -3249,19 +3249,19 @@
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="L38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -3272,7 +3272,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" s="3">
         <v>1993</v>
@@ -3282,19 +3282,19 @@
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="K39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="M39" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -3305,20 +3305,20 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C40" s="3">
         <v>1985</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="K40" s="2"/>
       <c r="L40" s="3"/>
@@ -3334,7 +3334,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C41" s="3">
         <v>1993</v>
@@ -3344,19 +3344,19 @@
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="K41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M41" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -3367,7 +3367,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C42" s="3">
         <v>1994</v>
@@ -3377,22 +3377,22 @@
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="K42" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
@@ -3403,7 +3403,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C43" s="3">
         <v>1995</v>
@@ -3413,22 +3413,22 @@
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="K43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="M43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
@@ -3439,7 +3439,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C44" s="3">
         <v>1995</v>
@@ -3449,22 +3449,22 @@
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="M44" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N44" s="3">
         <v>129</v>
@@ -3477,7 +3477,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C45" s="3">
         <v>1996</v>
@@ -3487,22 +3487,22 @@
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="L45" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -3513,7 +3513,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C46" s="3">
         <v>1996</v>
@@ -3523,19 +3523,19 @@
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="L46" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -3546,7 +3546,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C47" s="3">
         <v>1996</v>
@@ -3556,22 +3556,22 @@
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H47" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="K47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -3582,7 +3582,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C48" s="3">
         <v>1997</v>
@@ -3592,22 +3592,22 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>188</v>
-      </c>
       <c r="L48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N48" s="3">
         <v>53</v>
@@ -3620,20 +3620,20 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="3">
         <v>2008</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="3"/>
@@ -3649,7 +3649,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C50" s="3">
         <v>1997</v>
@@ -3659,19 +3659,19 @@
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="K50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L50" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M50" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N50" s="3">
         <v>141</v>
@@ -3684,20 +3684,20 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="3">
         <v>1984</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K51" s="2"/>
       <c r="L51" s="3"/>
@@ -3713,7 +3713,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C52" s="3">
         <v>1998</v>
@@ -3723,19 +3723,19 @@
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="K52" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="L52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
@@ -3746,20 +3746,20 @@
         <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C53" s="3">
         <v>1997</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K53" s="2"/>
       <c r="L53" s="3"/>
@@ -3775,7 +3775,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C54" s="3">
         <v>1998</v>
@@ -3785,22 +3785,22 @@
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="I54" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="K54" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K54" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="L54" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -3811,7 +3811,7 @@
         <v>55</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C55" s="3">
         <v>1999</v>
@@ -3821,19 +3821,19 @@
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="K55" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="K55" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="L55" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M55" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
@@ -3844,7 +3844,7 @@
         <v>56</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C56" s="3">
         <v>1999</v>
@@ -3854,19 +3854,19 @@
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="L56" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
@@ -3877,7 +3877,7 @@
         <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C57" s="3">
         <v>1999</v>
@@ -3887,19 +3887,19 @@
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="K57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M57" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
@@ -3910,7 +3910,7 @@
         <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C58" s="3">
         <v>2000</v>
@@ -3920,19 +3920,19 @@
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="K58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N58" s="3">
         <v>141</v>
@@ -3945,7 +3945,7 @@
         <v>59</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C59" s="3">
         <v>2001</v>
@@ -3955,28 +3955,28 @@
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="H59" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="I59" s="2" t="s">
+      <c r="J59" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="K59" s="2" t="s">
+      <c r="L59" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="M59" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N59" s="3">
         <v>83</v>
@@ -3993,7 +3993,7 @@
         <v>60</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="3">
         <v>2001</v>
@@ -4003,22 +4003,22 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="I60" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I60" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="K60" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="M60" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
@@ -4029,7 +4029,7 @@
         <v>61</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="3">
         <v>2001</v>
@@ -4039,19 +4039,19 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="L61" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
@@ -4062,7 +4062,7 @@
         <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C62" s="3">
         <v>2002</v>
@@ -4072,19 +4072,19 @@
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="K62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M62" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
@@ -4095,7 +4095,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C63" s="3">
         <v>2002</v>
@@ -4105,25 +4105,25 @@
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="L63" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M63" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
@@ -4134,7 +4134,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64" s="3">
         <v>2002</v>
@@ -4144,22 +4144,22 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="K64" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
@@ -4170,7 +4170,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C65" s="3">
         <v>2002</v>
@@ -4180,19 +4180,19 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="K65" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M65" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N65" s="3">
         <v>141</v>
@@ -4205,7 +4205,7 @@
         <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C66" s="3">
         <v>2003</v>
@@ -4215,19 +4215,19 @@
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G66" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="K66" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M66" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
@@ -4238,7 +4238,7 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C67" s="3">
         <v>2003</v>
@@ -4248,19 +4248,19 @@
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="K67" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N67" s="3">
         <v>141</v>
@@ -4273,7 +4273,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C68" s="3">
         <v>2004</v>
@@ -4283,19 +4283,19 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="K68" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M68" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
@@ -4306,7 +4306,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C69" s="3">
         <v>2004</v>
@@ -4316,19 +4316,19 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="K69" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="L69" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M69" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N69" s="3">
         <v>31</v>
@@ -4341,7 +4341,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C70" s="3">
         <v>2004</v>
@@ -4351,22 +4351,22 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="H70" s="2" t="s">
+      <c r="K70" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="L70" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M70" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
@@ -4377,7 +4377,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C71" s="3">
         <v>2005</v>
@@ -4387,19 +4387,19 @@
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="K71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="M71" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N71" s="3"/>
       <c r="O71" s="3"/>
@@ -4410,7 +4410,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C72" s="3">
         <v>2005</v>
@@ -4420,22 +4420,22 @@
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="I72" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="K72" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="L72" s="3" t="s">
+      <c r="M72" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
@@ -4446,7 +4446,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C73" s="3">
         <v>2006</v>
@@ -4456,19 +4456,19 @@
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="K73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N73" s="3">
         <v>124</v>
@@ -4481,7 +4481,7 @@
         <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C74" s="3">
         <v>2006</v>
@@ -4491,19 +4491,19 @@
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="K74" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N74" s="3"/>
       <c r="O74" s="3"/>
@@ -4514,7 +4514,7 @@
         <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C75" s="3">
         <v>2007</v>
@@ -4524,22 +4524,22 @@
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="H75" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="K75" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L75" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M75" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N75" s="3">
         <v>142</v>
@@ -4554,7 +4554,7 @@
         <v>78</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C76" s="3">
         <v>2007</v>
@@ -4564,19 +4564,19 @@
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="K76" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M76" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N76" s="3">
         <v>141</v>
@@ -4589,7 +4589,7 @@
         <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C77" s="3">
         <v>2008</v>
@@ -4599,19 +4599,19 @@
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="K77" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
@@ -4622,20 +4622,20 @@
         <v>80</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C78" s="3">
         <v>2009</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="K78" s="2"/>
       <c r="L78" s="3"/>
@@ -4651,20 +4651,20 @@
         <v>81</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C79" s="3">
         <v>2009</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="3"/>
@@ -4680,7 +4680,7 @@
         <v>82</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C80" s="3">
         <v>2009</v>
@@ -4690,19 +4690,19 @@
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="K80" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L80" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="L80" s="3" t="s">
+      <c r="M80" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
@@ -4713,7 +4713,7 @@
         <v>83</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C81" s="3">
         <v>2009</v>
@@ -4723,22 +4723,22 @@
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="I81" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K81" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="L81" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M81" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N81" s="3">
         <v>59</v>
@@ -4755,7 +4755,7 @@
         <v>84</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C82" s="3">
         <v>2009</v>
@@ -4765,22 +4765,22 @@
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="H82" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="H82" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="L82" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M82" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
@@ -4791,7 +4791,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C83" s="3">
         <v>2010</v>
@@ -4801,19 +4801,19 @@
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="K83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N83" s="3">
         <v>125</v>
@@ -4826,7 +4826,7 @@
         <v>86</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C84" s="3">
         <v>2011</v>
@@ -4836,19 +4836,19 @@
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K84" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="L84" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M84" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
@@ -4859,7 +4859,7 @@
         <v>87</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C85" s="3">
         <v>2011</v>
@@ -4869,19 +4869,19 @@
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="L85" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
@@ -4892,7 +4892,7 @@
         <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C86" s="3">
         <v>2011</v>
@@ -4902,22 +4902,22 @@
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="H86" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H86" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="K86" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L86" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M86" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
@@ -4928,7 +4928,7 @@
         <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C87" s="3">
         <v>2013</v>
@@ -4938,22 +4938,22 @@
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G87" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="G87" s="2" t="s">
+      <c r="I87" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="K87" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="M87" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N87" s="3">
         <v>135</v>
@@ -4966,7 +4966,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C88" s="3">
         <v>2013</v>
@@ -4976,22 +4976,22 @@
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G88" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="I88" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I88" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="K88" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L88" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M88" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
@@ -5002,7 +5002,7 @@
         <v>91</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C89" s="3">
         <v>2013</v>
@@ -5012,19 +5012,19 @@
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="K89" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="K89" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="L89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N89" s="3"/>
       <c r="O89" s="3"/>
@@ -5035,7 +5035,7 @@
         <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C90" s="3">
         <v>2013</v>
@@ -5045,19 +5045,19 @@
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="K90" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M90" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N90" s="3">
         <v>141</v>
@@ -5070,7 +5070,7 @@
         <v>93</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C91" s="3">
         <v>2014</v>
@@ -5080,19 +5080,19 @@
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="K91" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N91" s="3">
         <v>143</v>
@@ -5105,7 +5105,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C92" s="3">
         <v>2015</v>
@@ -5115,19 +5115,19 @@
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="K92" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M92" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
@@ -5138,7 +5138,7 @@
         <v>95</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C93" s="3">
         <v>2015</v>
@@ -5148,19 +5148,19 @@
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="K93" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M93" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
@@ -5171,7 +5171,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C94" s="3">
         <v>2015</v>
@@ -5181,19 +5181,19 @@
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="K94" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M94" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N94" s="3">
         <v>105</v>
@@ -5206,7 +5206,7 @@
         <v>97</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C95" s="3">
         <v>2015</v>
@@ -5216,22 +5216,22 @@
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="I95" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I95" s="2" t="s">
+      <c r="K95" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="K95" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="L95" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
@@ -5242,7 +5242,7 @@
         <v>99</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C96" s="3">
         <v>2016</v>
@@ -5252,19 +5252,19 @@
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="K96" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="K96" s="2" t="s">
-        <v>316</v>
-      </c>
       <c r="L96" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
@@ -5275,7 +5275,7 @@
         <v>100</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C97" s="3">
         <v>2016</v>
@@ -5285,22 +5285,22 @@
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G97" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="J97" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="J97" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="K97" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
@@ -5311,7 +5311,7 @@
         <v>101</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C98" s="3">
         <v>2016</v>
@@ -5321,19 +5321,19 @@
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="K98" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="K98" s="2" t="s">
+      <c r="L98" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="M98" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
@@ -5344,7 +5344,7 @@
         <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C99" s="3">
         <v>2017</v>
@@ -5354,19 +5354,19 @@
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="K99" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="L99" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
@@ -5377,7 +5377,7 @@
         <v>103</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C100" s="3">
         <v>2018</v>
@@ -5387,19 +5387,19 @@
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="K100" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M100" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
@@ -5410,7 +5410,7 @@
         <v>104</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C101" s="3">
         <v>2019</v>
@@ -5420,22 +5420,22 @@
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G101" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H101" s="2" t="s">
+      <c r="K101" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="K101" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="L101" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N101" s="3">
         <v>26</v>
@@ -5450,7 +5450,7 @@
         <v>105</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C102" s="3">
         <v>2020</v>
@@ -5460,19 +5460,19 @@
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="K102" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="N102" s="3">
         <v>96</v>
@@ -5485,7 +5485,7 @@
         <v>106</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C103" s="3">
         <v>2021</v>
@@ -5495,19 +5495,19 @@
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="K103" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L103" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L103" s="3" t="s">
+      <c r="M103" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
@@ -5518,7 +5518,7 @@
         <v>107</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C104" s="3">
         <v>2021</v>
@@ -5528,19 +5528,19 @@
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="G104" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="K104" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L104" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="M104" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
@@ -5551,7 +5551,7 @@
         <v>108</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C105" s="3">
         <v>2022</v>
@@ -5561,22 +5561,22 @@
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="I105" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="K105" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M105" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="M105" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="N105" s="3">
         <v>138</v>
@@ -5589,7 +5589,7 @@
         <v>109</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C106" s="3">
         <v>2022</v>
@@ -5599,25 +5599,25 @@
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="H106" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="K106" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="K106" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="L106" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M106" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="M106" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="N106" s="3">
         <v>138</v>
@@ -5630,7 +5630,7 @@
         <v>110</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C107" s="3">
         <v>2023</v>
@@ -5640,19 +5640,19 @@
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G107" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="K107" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="K107" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="L107" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
@@ -5663,7 +5663,7 @@
         <v>111</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C108" s="3">
         <v>2023</v>
@@ -5673,19 +5673,19 @@
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="K108" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="L108" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="M108" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="M108" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
@@ -5696,7 +5696,7 @@
         <v>112</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C109" s="3">
         <v>2023</v>
@@ -5706,19 +5706,19 @@
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="K109" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="K109" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="L109" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M109" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N109" s="3">
         <v>138</v>
@@ -5731,7 +5731,7 @@
         <v>113</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C110" s="3">
         <v>2023</v>
@@ -5741,19 +5741,19 @@
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="K110" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L110" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M110" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N110" s="3">
         <v>138</v>
@@ -5766,7 +5766,7 @@
         <v>114</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C111" s="3">
         <v>2024</v>
@@ -5776,19 +5776,19 @@
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="G111" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="K111" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L111" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M111" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="M111" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="N111" s="3">
         <v>138</v>
@@ -5801,7 +5801,7 @@
         <v>115</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C112" s="3">
         <v>2024</v>
@@ -5811,19 +5811,19 @@
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="K112" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M112" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="N112" s="3">
         <v>138</v>
@@ -5836,7 +5836,7 @@
         <v>116</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C113" s="3">
         <v>2025</v>
@@ -5846,22 +5846,22 @@
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="G113" s="2" t="s">
+      <c r="H113" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="H113" s="2" t="s">
+      <c r="K113" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="K113" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="L113" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M113" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="N113" s="3"/>
       <c r="O113" s="3"/>
@@ -5878,14 +5878,14 @@
         <v>1945</v>
       </c>
       <c r="D114" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E114" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="3"/>
@@ -5901,20 +5901,20 @@
         <v>120</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C115" s="3">
         <v>2007</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G115" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="3"/>
@@ -5936,14 +5936,14 @@
         <v>1973</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G116" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="3"/>
@@ -5965,14 +5965,14 @@
         <v>1969</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="3"/>
@@ -5990,17 +5990,17 @@
         <v>124</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C118" s="3">
         <v>2006</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G118" s="2"/>
       <c r="K118" s="2"/>
@@ -6017,23 +6017,23 @@
         <v>125</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C119" s="3">
         <v>2003</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G119" s="2" t="s">
+      <c r="H119" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="3"/>
@@ -6049,22 +6049,22 @@
         <v>127</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C120" s="3">
         <v>1986</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E120" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="G120" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="3"/>
@@ -6082,20 +6082,20 @@
         <v>128</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C121" s="3">
         <v>2011</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="3"/>
@@ -6111,20 +6111,20 @@
         <v>129</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C122" s="3">
         <v>1991</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="3"/>
@@ -6144,20 +6144,20 @@
         <v>130</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C123" s="3">
         <v>1991</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K123" s="2"/>
       <c r="L123" s="3"/>
@@ -6171,20 +6171,20 @@
         <v>132</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C124" s="3">
         <v>2010</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K124" s="2"/>
       <c r="L124" s="3"/>
@@ -6204,14 +6204,14 @@
         <v>1965</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K125" s="2"/>
       <c r="L125" s="3"/>
@@ -6225,20 +6225,20 @@
         <v>135</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C126" s="3">
         <v>2020</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K126" s="2"/>
       <c r="L126" s="3"/>
@@ -6264,14 +6264,14 @@
         <v>1929</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K127" s="2"/>
       <c r="L127" s="3"/>
@@ -6285,20 +6285,20 @@
         <v>138</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C128" s="3">
         <v>2022</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K128" s="2"/>
       <c r="L128" s="3"/>
@@ -6316,20 +6316,20 @@
         <v>139</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C129" s="3">
         <v>1983</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K129" s="2"/>
       <c r="L129" s="3"/>
@@ -6345,23 +6345,23 @@
         <v>141</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C130" s="3">
         <v>1997</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H130" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="K130" s="2"/>
       <c r="L130" s="3"/>
@@ -6381,20 +6381,20 @@
         <v>142</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C131" s="3">
         <v>2007</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="3"/>
@@ -6410,20 +6410,20 @@
         <v>143</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C132" s="3">
         <v>2014</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F132" s="3"/>
       <c r="G132" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="3"/>
@@ -6439,7 +6439,7 @@
         <v>144</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C133" s="3">
         <v>1986</v>
@@ -6449,22 +6449,22 @@
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="I133" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="I133" s="2" t="s">
+      <c r="K133" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="K133" s="2" t="s">
+      <c r="L133" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L133" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="M133" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N133" s="3">
         <v>127</v>
@@ -6479,7 +6479,7 @@
         <v>145</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C134" s="3">
         <v>2001</v>
@@ -6489,22 +6489,22 @@
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="G134" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="I134" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="I134" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="K134" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="L134" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L134" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="M134" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N134" s="3">
         <v>146</v>
@@ -6521,20 +6521,20 @@
         <v>146</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C135" s="3">
         <v>2011</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F135" s="3"/>
       <c r="G135" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K135" s="2"/>
       <c r="L135" s="3"/>
@@ -6552,20 +6552,20 @@
         <v>147</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C136" s="3">
         <v>2001</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F136" s="3"/>
       <c r="G136" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K136" s="2"/>
       <c r="L136" s="3"/>
@@ -6587,14 +6587,14 @@
         <v>1947</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F137" s="3"/>
       <c r="G137" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K137" s="2"/>
       <c r="L137" s="3"/>
@@ -6622,25 +6622,25 @@
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G138" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="G138" s="2" t="s">
+      <c r="I138" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="I138" s="2" t="s">
+      <c r="J138" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="J138" s="2" t="s">
-        <v>424</v>
-      </c>
       <c r="K138" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L138" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="N138" s="3">
         <v>148</v>
@@ -6661,16 +6661,16 @@
         <v>1957</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E139" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F139" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="G139" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="K139" s="2"/>
       <c r="L139" s="3"/>
@@ -6694,17 +6694,17 @@
         <v>1978</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F140" s="3"/>
       <c r="G140" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J140" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="K140" s="2"/>
       <c r="L140" s="3"/>
@@ -6720,20 +6720,20 @@
         <v>152</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C141" s="3">
         <v>2008</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F141" s="3"/>
       <c r="G141" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K141" s="2"/>
       <c r="L141" s="3"/>
@@ -6753,14 +6753,14 @@
         <v>1969</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F142" s="3"/>
       <c r="G142" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K142" s="2"/>
       <c r="L142" s="3"/>
@@ -6780,20 +6780,20 @@
         <v>154</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C143" s="3">
         <v>2003</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F143" s="3"/>
       <c r="G143" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K143" s="2"/>
       <c r="L143" s="3"/>
@@ -6809,22 +6809,22 @@
         <v>155</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C144" s="3">
         <v>2000</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E144" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="F144" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="G144" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="K144" s="2"/>
       <c r="L144" s="3"/>
@@ -6844,14 +6844,14 @@
         <v>1945</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F145" s="3"/>
       <c r="G145" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K145" s="2"/>
       <c r="L145" s="3"/>
@@ -6867,20 +6867,20 @@
         <v>157</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C146" s="3">
         <v>2022</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F146" s="3"/>
       <c r="G146" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K146" s="2"/>
       <c r="L146" s="3"/>
@@ -6900,14 +6900,14 @@
         <v>1973</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F147" s="3"/>
       <c r="G147" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K147" s="2"/>
       <c r="L147" s="3"/>
@@ -6921,20 +6921,20 @@
         <v>159</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C148" s="3">
         <v>2021</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F148" s="3"/>
       <c r="G148" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K148" s="2"/>
       <c r="L148" s="3"/>
@@ -6958,22 +6958,22 @@
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="G149" s="2" t="s">
+      <c r="J149" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="J149" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="K149" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="L149" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L149" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="M149" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N149" s="3">
         <v>161</v>
@@ -6986,20 +6986,20 @@
         <v>161</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C150" s="3">
         <v>1986</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F150" s="3"/>
       <c r="G150" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K150" s="2"/>
       <c r="L150" s="3"/>
@@ -7021,14 +7021,14 @@
         <v>1945</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K151" s="2"/>
       <c r="L151" s="3"/>

--- a/data/timeline.xlsx
+++ b/data/timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A6CDCA-98CF-4B46-8C46-B864A28769C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22B2C6B-F7ED-4057-813B-98F683EC8E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1465,7 +1465,7 @@
     <t>האיור של שולחן ה-Memex שפורסם במגזין Life בשנת 1945</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST!!!!!!!!! כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
+    <t xml:space="preserve">כלי נגינה אלקטרוני המאפשר לנגן מבלי לגעת בו פיזית. המשתמש מזיז את ידיו באוויר ליד שתי אנטנות, כאשר המרחק של יד אחת מהאנטנה שולט בגובה הצליל והיד השנייה שולטת בעוצמתו. כך תנועות הגוף במרחב מתורגמות ישירות לצליל, והוא נחשב לאחת הדוגמאות המוקדמות ביותר לאינטראקציה חשמלית המבוססת על מחוות ללא מגע.
 </t>
   </si>
 </sst>
@@ -1963,7 +1963,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="142.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
